--- a/salidas/empresas/UNP.xlsx
+++ b/salidas/empresas/UNP.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="EPS" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Info" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Mensual" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="EPS" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Acciones" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Info" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,13 +23,16 @@
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD"/>
   </numFmts>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -40,7 +43,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -48,12 +51,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
@@ -435,58 +447,58 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>fecha</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>precio_ajustado</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>precio_cierre</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>volumen</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>pe</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>acciones_circulacion</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>market_cap</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>rotacion</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.49657440185547</v>
+        <v>14.49657344818115</v>
       </c>
       <c r="C2" t="n">
         <v>22.11499977111816</v>
@@ -501,11 +513,11 @@
       <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51131629943848</v>
+        <v>14.51131725311279</v>
       </c>
       <c r="C3" t="n">
         <v>22.13750076293945</v>
@@ -520,11 +532,11 @@
       <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>15.34920024871826</v>
+        <v>15.349196434021</v>
       </c>
       <c r="C4" t="n">
         <v>23.33749961853027</v>
@@ -539,11 +551,11 @@
       <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.99732875823975</v>
+        <v>14.99732112884521</v>
       </c>
       <c r="C5" t="n">
         <v>22.80249977111816</v>
@@ -558,11 +570,11 @@
       <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.30849075317383</v>
+        <v>15.30848026275635</v>
       </c>
       <c r="C6" t="n">
         <v>23.20000076293945</v>
@@ -577,11 +589,11 @@
       <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33487796783447</v>
+        <v>15.33487892150879</v>
       </c>
       <c r="C7" t="n">
         <v>23.23999977111816</v>
@@ -596,7 +608,7 @@
       <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>38929</v>
       </c>
       <c r="B8" t="n">
@@ -615,11 +627,11 @@
       <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>13.3041934967041</v>
+        <v>13.30419158935547</v>
       </c>
       <c r="C9" t="n">
         <v>20.08749961853027</v>
@@ -634,11 +646,11 @@
       <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>38990</v>
       </c>
       <c r="B10" t="n">
-        <v>14.57086277008057</v>
+        <v>14.57085990905762</v>
       </c>
       <c r="C10" t="n">
         <v>22</v>
@@ -653,11 +665,11 @@
       <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.00633907318115</v>
+        <v>15.0063362121582</v>
       </c>
       <c r="C11" t="n">
         <v>22.65749931335449</v>
@@ -672,7 +684,7 @@
       <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>39051</v>
       </c>
       <c r="B12" t="n">
@@ -691,11 +703,11 @@
       <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>15.28700637817383</v>
+        <v>15.2870044708252</v>
       </c>
       <c r="C13" t="n">
         <v>23.0049991607666</v>
@@ -710,11 +722,11 @@
       <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>16.77882766723633</v>
+        <v>16.7788257598877</v>
       </c>
       <c r="C14" t="n">
         <v>25.25</v>
@@ -729,11 +741,11 @@
       <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.43215751647949</v>
+        <v>16.43215370178223</v>
       </c>
       <c r="C15" t="n">
         <v>24.64500045776367</v>
@@ -748,11 +760,11 @@
       <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>39172</v>
       </c>
       <c r="B16" t="n">
-        <v>16.92722320556641</v>
+        <v>16.92723274230957</v>
       </c>
       <c r="C16" t="n">
         <v>25.38750076293945</v>
@@ -767,11 +779,11 @@
       <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>19.04417610168457</v>
+        <v>19.04416847229004</v>
       </c>
       <c r="C17" t="n">
         <v>28.5625</v>
@@ -786,11 +798,11 @@
       <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>20.17620086669922</v>
+        <v>20.17619705200195</v>
       </c>
       <c r="C18" t="n">
         <v>30.17000007629395</v>
@@ -805,7 +817,7 @@
       <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>39263</v>
       </c>
       <c r="B19" t="n">
@@ -824,11 +836,11 @@
       <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.91872978210449</v>
+        <v>19.91873359680176</v>
       </c>
       <c r="C20" t="n">
         <v>29.78499984741211</v>
@@ -843,11 +855,11 @@
       <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>18.71292686462402</v>
+        <v>18.71293067932129</v>
       </c>
       <c r="C21" t="n">
         <v>27.89249992370605</v>
@@ -862,7 +874,7 @@
       <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>39355</v>
       </c>
       <c r="B22" t="n">
@@ -881,7 +893,7 @@
       <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>39386</v>
       </c>
       <c r="B23" t="n">
@@ -900,11 +912,11 @@
       <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.2336540222168</v>
+        <v>21.23364448547363</v>
       </c>
       <c r="C24" t="n">
         <v>31.53499984741211</v>
@@ -919,11 +931,11 @@
       <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>21.14612197875977</v>
+        <v>21.1461181640625</v>
       </c>
       <c r="C25" t="n">
         <v>31.40500068664551</v>
@@ -938,11 +950,11 @@
       <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>21.00135040283203</v>
+        <v>21.0013484954834</v>
       </c>
       <c r="C26" t="n">
         <v>31.19000053405762</v>
@@ -957,11 +969,11 @@
       <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.00135040283203</v>
+        <v>21.0013484954834</v>
       </c>
       <c r="C27" t="n">
         <v>31.19000053405762</v>
@@ -976,11 +988,11 @@
       <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>21.18360900878906</v>
+        <v>21.18361663818359</v>
       </c>
       <c r="C28" t="n">
         <v>31.34499931335449</v>
@@ -995,11 +1007,11 @@
       <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>24.53061866760254</v>
+        <v>24.5306224822998</v>
       </c>
       <c r="C29" t="n">
         <v>36.29750061035156</v>
@@ -1014,11 +1026,11 @@
       <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>27.81341934204102</v>
+        <v>27.81341361999512</v>
       </c>
       <c r="C30" t="n">
         <v>41.15499877929688</v>
@@ -1033,11 +1045,11 @@
       <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.58285331726074</v>
+        <v>25.58285140991211</v>
       </c>
       <c r="C31" t="n">
         <v>37.75</v>
@@ -1052,11 +1064,11 @@
       <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.93444442749023</v>
+        <v>27.93444633483887</v>
       </c>
       <c r="C32" t="n">
         <v>41.22000122070312</v>
@@ -1071,11 +1083,11 @@
       <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.52409934997559</v>
+        <v>28.52408790588379</v>
       </c>
       <c r="C33" t="n">
         <v>41.95000076293945</v>
@@ -1090,11 +1102,11 @@
       <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.19278907775879</v>
+        <v>24.19277572631836</v>
       </c>
       <c r="C34" t="n">
         <v>35.58000183105469</v>
@@ -1109,11 +1121,11 @@
       <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>22.70028114318848</v>
+        <v>22.70028877258301</v>
       </c>
       <c r="C35" t="n">
         <v>33.3849983215332</v>
@@ -1128,11 +1140,11 @@
       <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.10478973388672</v>
+        <v>17.10479545593262</v>
       </c>
       <c r="C36" t="n">
         <v>25.02000045776367</v>
@@ -1147,11 +1159,11 @@
       <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.33910751342773</v>
+        <v>16.33911895751953</v>
       </c>
       <c r="C37" t="n">
         <v>23.89999961853027</v>
@@ -1166,11 +1178,11 @@
       <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>14.96840667724609</v>
+        <v>14.96840572357178</v>
       </c>
       <c r="C38" t="n">
         <v>21.89500045776367</v>
@@ -1185,11 +1197,11 @@
       <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.91257572174072</v>
+        <v>12.91257858276367</v>
       </c>
       <c r="C39" t="n">
         <v>18.76000022888184</v>
@@ -1204,11 +1216,11 @@
       <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.14808940887451</v>
+        <v>14.14808464050293</v>
       </c>
       <c r="C40" t="n">
         <v>20.55500030517578</v>
@@ -1223,11 +1235,11 @@
       <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.91162490844727</v>
+        <v>16.91162109375</v>
       </c>
       <c r="C41" t="n">
         <v>24.56999969482422</v>
@@ -1242,11 +1254,11 @@
       <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>17.05248069763184</v>
+        <v>17.0524845123291</v>
       </c>
       <c r="C42" t="n">
         <v>24.63500022888184</v>
@@ -1261,11 +1273,11 @@
       <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>39994</v>
       </c>
       <c r="B43" t="n">
-        <v>18.01810646057129</v>
+        <v>18.01810073852539</v>
       </c>
       <c r="C43" t="n">
         <v>26.03000068664551</v>
@@ -1280,7 +1292,7 @@
       <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>40025</v>
       </c>
       <c r="B44" t="n">
@@ -1305,11 +1317,11 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.79338836669922</v>
+        <v>20.79338645935059</v>
       </c>
       <c r="C45" t="n">
         <v>29.90500068664551</v>
@@ -1330,7 +1342,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>40086</v>
       </c>
       <c r="B46" t="n">
@@ -1355,11 +1367,11 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>19.16982269287109</v>
+        <v>19.16982460021973</v>
       </c>
       <c r="C47" t="n">
         <v>27.56999969482422</v>
@@ -1380,11 +1392,11 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.08537864685059</v>
+        <v>22.08538055419922</v>
       </c>
       <c r="C48" t="n">
         <v>31.6299991607666</v>
@@ -1405,11 +1417,11 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.3088207244873</v>
+        <v>22.30881690979004</v>
       </c>
       <c r="C49" t="n">
         <v>31.95000076293945</v>
@@ -1430,11 +1442,11 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.12180709838867</v>
+        <v>21.12180519104004</v>
       </c>
       <c r="C50" t="n">
         <v>30.25</v>
@@ -1455,7 +1467,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>40237</v>
       </c>
       <c r="B51" t="n">
@@ -1480,11 +1492,11 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>25.69506072998047</v>
+        <v>25.69505500793457</v>
       </c>
       <c r="C52" t="n">
         <v>36.65000152587891</v>
@@ -1505,11 +1517,11 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>26.52234268188477</v>
+        <v>26.52234840393066</v>
       </c>
       <c r="C53" t="n">
         <v>37.83000183105469</v>
@@ -1530,11 +1542,11 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>25.16061401367188</v>
+        <v>25.16061782836914</v>
       </c>
       <c r="C54" t="n">
         <v>35.71500015258789</v>
@@ -1555,11 +1567,11 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.48431396484375</v>
+        <v>24.48431777954102</v>
       </c>
       <c r="C55" t="n">
         <v>34.75500106811523</v>
@@ -1580,11 +1592,11 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.30188369750977</v>
+        <v>26.30188941955566</v>
       </c>
       <c r="C56" t="n">
         <v>37.33499908447266</v>
@@ -1605,7 +1617,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>40421</v>
       </c>
       <c r="B57" t="n">
@@ -1630,11 +1642,11 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.94527816772461</v>
+        <v>28.94528388977051</v>
       </c>
       <c r="C58" t="n">
         <v>40.90000152587891</v>
@@ -1655,11 +1667,11 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>31.02593803405762</v>
+        <v>31.02594184875488</v>
       </c>
       <c r="C59" t="n">
         <v>43.84000015258789</v>
@@ -1680,11 +1692,11 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.01989364624023</v>
+        <v>32.01988220214844</v>
       </c>
       <c r="C60" t="n">
         <v>45.05500030517578</v>
@@ -1705,7 +1717,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>40543</v>
       </c>
       <c r="B61" t="n">
@@ -1730,11 +1742,11 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>33.62604141235352</v>
+        <v>33.62602233886719</v>
       </c>
       <c r="C62" t="n">
         <v>47.31499862670898</v>
@@ -1755,7 +1767,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>40602</v>
       </c>
       <c r="B63" t="n">
@@ -1784,11 +1796,11 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>35.08488464355469</v>
+        <v>35.08487701416016</v>
       </c>
       <c r="C64" t="n">
         <v>49.16500091552734</v>
@@ -1813,11 +1825,11 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.91885757446289</v>
+        <v>36.91886138916016</v>
       </c>
       <c r="C65" t="n">
         <v>51.73500061035156</v>
@@ -1842,11 +1854,11 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>37.62830352783203</v>
+        <v>37.6283073425293</v>
       </c>
       <c r="C66" t="n">
         <v>52.48500061035156</v>
@@ -1871,11 +1883,11 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.42398452758789</v>
+        <v>37.42399215698242</v>
       </c>
       <c r="C67" t="n">
         <v>52.20000076293945</v>
@@ -1900,7 +1912,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>40755</v>
       </c>
       <c r="B68" t="n">
@@ -1929,11 +1941,11 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>33.21612548828125</v>
+        <v>33.21611404418945</v>
       </c>
       <c r="C69" t="n">
         <v>46.08499908447266</v>
@@ -1958,11 +1970,11 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>29.43212509155273</v>
+        <v>29.43213653564453</v>
       </c>
       <c r="C70" t="n">
         <v>40.83499908447266</v>
@@ -1987,11 +1999,11 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>35.8829231262207</v>
+        <v>35.88291549682617</v>
       </c>
       <c r="C71" t="n">
         <v>49.78499984741211</v>
@@ -2016,7 +2028,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>40877</v>
       </c>
       <c r="B72" t="n">
@@ -2045,11 +2057,11 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>38.42078018188477</v>
+        <v>38.42077255249023</v>
       </c>
       <c r="C73" t="n">
         <v>52.97000122070312</v>
@@ -2074,7 +2086,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="1" t="n">
+      <c r="A74" s="2" t="n">
         <v>40939</v>
       </c>
       <c r="B74" t="n">
@@ -2103,7 +2115,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="1" t="n">
+      <c r="A75" s="2" t="n">
         <v>40968</v>
       </c>
       <c r="B75" t="n">
@@ -2132,7 +2144,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="1" t="n">
+      <c r="A76" s="2" t="n">
         <v>40999</v>
       </c>
       <c r="B76" t="n">
@@ -2161,11 +2173,11 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="1" t="n">
+      <c r="A77" s="2" t="n">
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>40.99653244018555</v>
+        <v>40.99651718139648</v>
       </c>
       <c r="C77" t="n">
         <v>56.22000122070312</v>
@@ -2190,11 +2202,11 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="1" t="n">
+      <c r="A78" s="2" t="n">
         <v>41060</v>
       </c>
       <c r="B78" t="n">
-        <v>40.83633422851562</v>
+        <v>40.83633041381836</v>
       </c>
       <c r="C78" t="n">
         <v>55.70000076293945</v>
@@ -2219,11 +2231,11 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="1" t="n">
+      <c r="A79" s="2" t="n">
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>43.73591613769531</v>
+        <v>43.73594284057617</v>
       </c>
       <c r="C79" t="n">
         <v>59.65499877929688</v>
@@ -2248,11 +2260,11 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="1" t="n">
+      <c r="A80" s="2" t="n">
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>44.94561767578125</v>
+        <v>44.94563674926758</v>
       </c>
       <c r="C80" t="n">
         <v>61.30500030517578</v>
@@ -2277,11 +2289,11 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="1" t="n">
+      <c r="A81" s="2" t="n">
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.73407745361328</v>
+        <v>44.73406600952148</v>
       </c>
       <c r="C81" t="n">
         <v>60.72000122070312</v>
@@ -2306,11 +2318,11 @@
       </c>
     </row>
     <row r="82">
-      <c r="A82" s="1" t="n">
+      <c r="A82" s="2" t="n">
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.7247428894043</v>
+        <v>43.72475051879883</v>
       </c>
       <c r="C82" t="n">
         <v>59.34999847412109</v>
@@ -2335,11 +2347,11 @@
       </c>
     </row>
     <row r="83">
-      <c r="A83" s="1" t="n">
+      <c r="A83" s="2" t="n">
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>45.31976699829102</v>
+        <v>45.31975173950195</v>
       </c>
       <c r="C83" t="n">
         <v>61.51499938964844</v>
@@ -2364,11 +2376,11 @@
       </c>
     </row>
     <row r="84">
-      <c r="A84" s="1" t="n">
+      <c r="A84" s="2" t="n">
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.48439788818359</v>
+        <v>45.4843864440918</v>
       </c>
       <c r="C84" t="n">
         <v>61.38999938964844</v>
@@ -2393,11 +2405,11 @@
       </c>
     </row>
     <row r="85">
-      <c r="A85" s="1" t="n">
+      <c r="A85" s="2" t="n">
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>46.57352828979492</v>
+        <v>46.57352066040039</v>
       </c>
       <c r="C85" t="n">
         <v>62.86000061035156</v>
@@ -2422,11 +2434,11 @@
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="1" t="n">
+      <c r="A86" s="2" t="n">
         <v>41305</v>
       </c>
       <c r="B86" t="n">
-        <v>48.69994735717773</v>
+        <v>48.6999397277832</v>
       </c>
       <c r="C86" t="n">
         <v>65.73000335693359</v>
@@ -2451,11 +2463,11 @@
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="1" t="n">
+      <c r="A87" s="2" t="n">
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>51.05751419067383</v>
+        <v>51.05752182006836</v>
       </c>
       <c r="C87" t="n">
         <v>68.55500030517578</v>
@@ -2480,11 +2492,11 @@
       </c>
     </row>
     <row r="88">
-      <c r="A88" s="1" t="n">
+      <c r="A88" s="2" t="n">
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>53.03115844726562</v>
+        <v>53.03116226196289</v>
       </c>
       <c r="C88" t="n">
         <v>71.20500183105469</v>
@@ -2509,11 +2521,11 @@
       </c>
     </row>
     <row r="89">
-      <c r="A89" s="1" t="n">
+      <c r="A89" s="2" t="n">
         <v>41394</v>
       </c>
       <c r="B89" t="n">
-        <v>55.09790420532227</v>
+        <v>55.09789276123047</v>
       </c>
       <c r="C89" t="n">
         <v>73.98000335693359</v>
@@ -2538,11 +2550,11 @@
       </c>
     </row>
     <row r="90">
-      <c r="A90" s="1" t="n">
+      <c r="A90" s="2" t="n">
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.83093643188477</v>
+        <v>57.83095169067383</v>
       </c>
       <c r="C90" t="n">
         <v>77.30999755859375</v>
@@ -2567,11 +2579,11 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="1" t="n">
+      <c r="A91" s="2" t="n">
         <v>41455</v>
       </c>
       <c r="B91" t="n">
-        <v>57.70377731323242</v>
+        <v>57.70377349853516</v>
       </c>
       <c r="C91" t="n">
         <v>77.13999938964844</v>
@@ -2596,11 +2608,11 @@
       </c>
     </row>
     <row r="92">
-      <c r="A92" s="1" t="n">
+      <c r="A92" s="2" t="n">
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.3157844543457</v>
+        <v>59.31579971313477</v>
       </c>
       <c r="C92" t="n">
         <v>79.29499816894531</v>
@@ -2625,11 +2637,11 @@
       </c>
     </row>
     <row r="93">
-      <c r="A93" s="1" t="n">
+      <c r="A93" s="2" t="n">
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.72389221191406</v>
+        <v>57.72389984130859</v>
       </c>
       <c r="C93" t="n">
         <v>76.76999664306641</v>
@@ -2654,11 +2666,11 @@
       </c>
     </row>
     <row r="94">
-      <c r="A94" s="1" t="n">
+      <c r="A94" s="2" t="n">
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.40061950683594</v>
+        <v>58.40061569213867</v>
       </c>
       <c r="C94" t="n">
         <v>77.66999816894531</v>
@@ -2683,11 +2695,11 @@
       </c>
     </row>
     <row r="95">
-      <c r="A95" s="1" t="n">
+      <c r="A95" s="2" t="n">
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>56.91936874389648</v>
+        <v>56.91934967041016</v>
       </c>
       <c r="C95" t="n">
         <v>75.69999694824219</v>
@@ -2712,11 +2724,11 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" s="1" t="n">
+      <c r="A96" s="2" t="n">
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>61.21648025512695</v>
+        <v>61.21649551391602</v>
       </c>
       <c r="C96" t="n">
         <v>81.01999664306641</v>
@@ -2741,7 +2753,7 @@
       </c>
     </row>
     <row r="97">
-      <c r="A97" s="1" t="n">
+      <c r="A97" s="2" t="n">
         <v>41639</v>
       </c>
       <c r="B97" t="n">
@@ -2770,11 +2782,11 @@
       </c>
     </row>
     <row r="98">
-      <c r="A98" s="1" t="n">
+      <c r="A98" s="2" t="n">
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>65.82548522949219</v>
+        <v>65.82549285888672</v>
       </c>
       <c r="C98" t="n">
         <v>87.12000274658203</v>
@@ -2799,11 +2811,11 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="1" t="n">
+      <c r="A99" s="2" t="n">
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.49390411376953</v>
+        <v>68.49392700195312</v>
       </c>
       <c r="C99" t="n">
         <v>90.19000244140625</v>
@@ -2828,11 +2840,11 @@
       </c>
     </row>
     <row r="100">
-      <c r="A100" s="1" t="n">
+      <c r="A100" s="2" t="n">
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>71.25826263427734</v>
+        <v>71.25825500488281</v>
       </c>
       <c r="C100" t="n">
         <v>93.83000183105469</v>
@@ -2857,11 +2869,11 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="1" t="n">
+      <c r="A101" s="2" t="n">
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>72.31005859375</v>
+        <v>72.31005096435547</v>
       </c>
       <c r="C101" t="n">
         <v>95.21499633789062</v>
@@ -2886,11 +2898,11 @@
       </c>
     </row>
     <row r="102">
-      <c r="A102" s="1" t="n">
+      <c r="A102" s="2" t="n">
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.66678619384766</v>
+        <v>75.66680908203125</v>
       </c>
       <c r="C102" t="n">
         <v>99.63500213623047</v>
@@ -2915,11 +2927,11 @@
       </c>
     </row>
     <row r="103">
-      <c r="A103" s="1" t="n">
+      <c r="A103" s="2" t="n">
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>76.09297180175781</v>
+        <v>76.09297943115234</v>
       </c>
       <c r="C103" t="n">
         <v>99.75</v>
@@ -2944,11 +2956,11 @@
       </c>
     </row>
     <row r="104">
-      <c r="A104" s="1" t="n">
+      <c r="A104" s="2" t="n">
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.99448394775391</v>
+        <v>74.99449920654297</v>
       </c>
       <c r="C104" t="n">
         <v>98.30999755859375</v>
@@ -2973,7 +2985,7 @@
       </c>
     </row>
     <row r="105">
-      <c r="A105" s="1" t="n">
+      <c r="A105" s="2" t="n">
         <v>41882</v>
       </c>
       <c r="B105" t="n">
@@ -3002,7 +3014,7 @@
       </c>
     </row>
     <row r="106">
-      <c r="A106" s="1" t="n">
+      <c r="A106" s="2" t="n">
         <v>41912</v>
       </c>
       <c r="B106" t="n">
@@ -3031,11 +3043,11 @@
       </c>
     </row>
     <row r="107">
-      <c r="A107" s="1" t="n">
+      <c r="A107" s="2" t="n">
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>89.25511169433594</v>
+        <v>89.255126953125</v>
       </c>
       <c r="C107" t="n">
         <v>116.4499969482422</v>
@@ -3060,11 +3072,11 @@
       </c>
     </row>
     <row r="108">
-      <c r="A108" s="1" t="n">
+      <c r="A108" s="2" t="n">
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>89.86475372314453</v>
+        <v>89.86479187011719</v>
       </c>
       <c r="C108" t="n">
         <v>116.7699966430664</v>
@@ -3089,11 +3101,11 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="1" t="n">
+      <c r="A109" s="2" t="n">
         <v>42004</v>
       </c>
       <c r="B109" t="n">
-        <v>91.68097686767578</v>
+        <v>91.68099212646484</v>
       </c>
       <c r="C109" t="n">
         <v>119.129997253418</v>
@@ -3118,11 +3130,11 @@
       </c>
     </row>
     <row r="110">
-      <c r="A110" s="1" t="n">
+      <c r="A110" s="2" t="n">
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>90.20340728759766</v>
+        <v>90.20339202880859</v>
       </c>
       <c r="C110" t="n">
         <v>117.2099990844727</v>
@@ -3147,11 +3159,11 @@
       </c>
     </row>
     <row r="111">
-      <c r="A111" s="1" t="n">
+      <c r="A111" s="2" t="n">
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>92.96739196777344</v>
+        <v>92.96739959716797</v>
       </c>
       <c r="C111" t="n">
         <v>120.2600021362305</v>
@@ -3176,11 +3188,11 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="1" t="n">
+      <c r="A112" s="2" t="n">
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>83.72941589355469</v>
+        <v>83.72939300537109</v>
       </c>
       <c r="C112" t="n">
         <v>108.3099975585938</v>
@@ -3205,11 +3217,11 @@
       </c>
     </row>
     <row r="113">
-      <c r="A113" s="1" t="n">
+      <c r="A113" s="2" t="n">
         <v>42124</v>
       </c>
       <c r="B113" t="n">
-        <v>82.12147521972656</v>
+        <v>82.1214599609375</v>
       </c>
       <c r="C113" t="n">
         <v>106.2300033569336</v>
@@ -3234,11 +3246,11 @@
       </c>
     </row>
     <row r="114">
-      <c r="A114" s="1" t="n">
+      <c r="A114" s="2" t="n">
         <v>42155</v>
       </c>
       <c r="B114" t="n">
-        <v>78.42800140380859</v>
+        <v>78.42800903320312</v>
       </c>
       <c r="C114" t="n">
         <v>100.9100036621094</v>
@@ -3263,11 +3275,11 @@
       </c>
     </row>
     <row r="115">
-      <c r="A115" s="1" t="n">
+      <c r="A115" s="2" t="n">
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>74.12227630615234</v>
+        <v>74.12226867675781</v>
       </c>
       <c r="C115" t="n">
         <v>95.37000274658203</v>
@@ -3292,11 +3304,11 @@
       </c>
     </row>
     <row r="116">
-      <c r="A116" s="1" t="n">
+      <c r="A116" s="2" t="n">
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>75.84767150878906</v>
+        <v>75.84769439697266</v>
       </c>
       <c r="C116" t="n">
         <v>97.58999633789062</v>
@@ -3321,11 +3333,11 @@
       </c>
     </row>
     <row r="117">
-      <c r="A117" s="1" t="n">
+      <c r="A117" s="2" t="n">
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>67.07642364501953</v>
+        <v>67.07646179199219</v>
       </c>
       <c r="C117" t="n">
         <v>85.73999786376953</v>
@@ -3350,11 +3362,11 @@
       </c>
     </row>
     <row r="118">
-      <c r="A118" s="1" t="n">
+      <c r="A118" s="2" t="n">
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.16527557373047</v>
+        <v>69.16525268554688</v>
       </c>
       <c r="C118" t="n">
         <v>88.41000366210938</v>
@@ -3379,11 +3391,11 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="1" t="n">
+      <c r="A119" s="2" t="n">
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>69.90061950683594</v>
+        <v>69.90065002441406</v>
       </c>
       <c r="C119" t="n">
         <v>89.34999847412109</v>
@@ -3408,11 +3420,11 @@
       </c>
     </row>
     <row r="120">
-      <c r="A120" s="1" t="n">
+      <c r="A120" s="2" t="n">
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>66.10481262207031</v>
+        <v>66.10480499267578</v>
       </c>
       <c r="C120" t="n">
         <v>83.94999694824219</v>
@@ -3437,11 +3449,11 @@
       </c>
     </row>
     <row r="121">
-      <c r="A121" s="1" t="n">
+      <c r="A121" s="2" t="n">
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>61.57709121704102</v>
+        <v>61.57709503173828</v>
       </c>
       <c r="C121" t="n">
         <v>78.19999694824219</v>
@@ -3466,11 +3478,11 @@
       </c>
     </row>
     <row r="122">
-      <c r="A122" s="1" t="n">
+      <c r="A122" s="2" t="n">
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>56.69502639770508</v>
+        <v>56.69500732421875</v>
       </c>
       <c r="C122" t="n">
         <v>72</v>
@@ -3495,11 +3507,11 @@
       </c>
     </row>
     <row r="123">
-      <c r="A123" s="1" t="n">
+      <c r="A123" s="2" t="n">
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>62.52618789672852</v>
+        <v>62.52619552612305</v>
       </c>
       <c r="C123" t="n">
         <v>78.86000061035156</v>
@@ -3524,11 +3536,11 @@
       </c>
     </row>
     <row r="124">
-      <c r="A124" s="1" t="n">
+      <c r="A124" s="2" t="n">
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>63.07328033447266</v>
+        <v>63.07326507568359</v>
       </c>
       <c r="C124" t="n">
         <v>79.55000305175781</v>
@@ -3553,11 +3565,11 @@
       </c>
     </row>
     <row r="125">
-      <c r="A125" s="1" t="n">
+      <c r="A125" s="2" t="n">
         <v>42490</v>
       </c>
       <c r="B125" t="n">
-        <v>69.16258239746094</v>
+        <v>69.16255950927734</v>
       </c>
       <c r="C125" t="n">
         <v>87.23000335693359</v>
@@ -3582,11 +3594,11 @@
       </c>
     </row>
     <row r="126">
-      <c r="A126" s="1" t="n">
+      <c r="A126" s="2" t="n">
         <v>42521</v>
       </c>
       <c r="B126" t="n">
-        <v>67.19800567626953</v>
+        <v>67.19797515869141</v>
       </c>
       <c r="C126" t="n">
         <v>84.19000244140625</v>
@@ -3611,11 +3623,11 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="1" t="n">
+      <c r="A127" s="2" t="n">
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>69.640380859375</v>
+        <v>69.64038848876953</v>
       </c>
       <c r="C127" t="n">
         <v>87.25</v>
@@ -3640,11 +3652,11 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="1" t="n">
+      <c r="A128" s="2" t="n">
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>74.26978302001953</v>
+        <v>74.26976013183594</v>
       </c>
       <c r="C128" t="n">
         <v>93.05000305175781</v>
@@ -3669,11 +3681,11 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="1" t="n">
+      <c r="A129" s="2" t="n">
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>76.69268035888672</v>
+        <v>76.69265747070312</v>
       </c>
       <c r="C129" t="n">
         <v>95.52999877929688</v>
@@ -3698,7 +3710,7 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="1" t="n">
+      <c r="A130" s="2" t="n">
         <v>42643</v>
       </c>
       <c r="B130" t="n">
@@ -3727,11 +3739,11 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="1" t="n">
+      <c r="A131" s="2" t="n">
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>70.79203796386719</v>
+        <v>70.7919921875</v>
       </c>
       <c r="C131" t="n">
         <v>88.18000030517578</v>
@@ -3756,11 +3768,11 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="1" t="n">
+      <c r="A132" s="2" t="n">
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>81.83392333984375</v>
+        <v>81.83391571044922</v>
       </c>
       <c r="C132" t="n">
         <v>101.3300018310547</v>
@@ -3785,11 +3797,11 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="1" t="n">
+      <c r="A133" s="2" t="n">
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>83.73178863525391</v>
+        <v>83.73176574707031</v>
       </c>
       <c r="C133" t="n">
         <v>103.6800003051758</v>
@@ -3814,7 +3826,7 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="1" t="n">
+      <c r="A134" s="2" t="n">
         <v>42766</v>
       </c>
       <c r="B134" t="n">
@@ -3843,11 +3855,11 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="1" t="n">
+      <c r="A135" s="2" t="n">
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>87.66925811767578</v>
+        <v>87.66921997070312</v>
       </c>
       <c r="C135" t="n">
         <v>107.9400024414062</v>
@@ -3872,11 +3884,11 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="1" t="n">
+      <c r="A136" s="2" t="n">
         <v>42825</v>
       </c>
       <c r="B136" t="n">
-        <v>86.02857971191406</v>
+        <v>86.02858734130859</v>
       </c>
       <c r="C136" t="n">
         <v>105.9199981689453</v>
@@ -3901,11 +3913,11 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="1" t="n">
+      <c r="A137" s="2" t="n">
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>90.93428039550781</v>
+        <v>90.93428802490234</v>
       </c>
       <c r="C137" t="n">
         <v>111.9599990844727</v>
@@ -3930,11 +3942,11 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="1" t="n">
+      <c r="A138" s="2" t="n">
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>90.08284759521484</v>
+        <v>90.08285522460938</v>
       </c>
       <c r="C138" t="n">
         <v>110.3000030517578</v>
@@ -3959,11 +3971,11 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="1" t="n">
+      <c r="A139" s="2" t="n">
         <v>42916</v>
       </c>
       <c r="B139" t="n">
-        <v>88.94760894775391</v>
+        <v>88.9476318359375</v>
       </c>
       <c r="C139" t="n">
         <v>108.9100036621094</v>
@@ -3988,11 +4000,11 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="1" t="n">
+      <c r="A140" s="2" t="n">
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>84.08820343017578</v>
+        <v>84.08824157714844</v>
       </c>
       <c r="C140" t="n">
         <v>102.9599990844727</v>
@@ -4017,11 +4029,11 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="1" t="n">
+      <c r="A141" s="2" t="n">
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>86.49987030029297</v>
+        <v>86.4998779296875</v>
       </c>
       <c r="C141" t="n">
         <v>105.3000030517578</v>
@@ -4046,11 +4058,11 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="1" t="n">
+      <c r="A142" s="2" t="n">
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>95.26484680175781</v>
+        <v>95.26486206054688</v>
       </c>
       <c r="C142" t="n">
         <v>115.9700012207031</v>
@@ -4075,11 +4087,11 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="1" t="n">
+      <c r="A143" s="2" t="n">
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>95.11697387695312</v>
+        <v>95.11698150634766</v>
       </c>
       <c r="C143" t="n">
         <v>115.7900009155273</v>
@@ -4104,11 +4116,11 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="1" t="n">
+      <c r="A144" s="2" t="n">
         <v>43069</v>
       </c>
       <c r="B144" t="n">
-        <v>104.4997863769531</v>
+        <v>104.4997940063477</v>
       </c>
       <c r="C144" t="n">
         <v>126.5</v>
@@ -4133,11 +4145,11 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="1" t="n">
+      <c r="A145" s="2" t="n">
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>110.7780685424805</v>
+        <v>110.7780380249023</v>
       </c>
       <c r="C145" t="n">
         <v>134.1000061035156</v>
@@ -4162,11 +4174,11 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="1" t="n">
+      <c r="A146" s="2" t="n">
         <v>43131</v>
       </c>
       <c r="B146" t="n">
-        <v>110.2824020385742</v>
+        <v>110.2823638916016</v>
       </c>
       <c r="C146" t="n">
         <v>133.5</v>
@@ -4191,11 +4203,11 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="1" t="n">
+      <c r="A147" s="2" t="n">
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>108.1665115356445</v>
+        <v>108.1665496826172</v>
       </c>
       <c r="C147" t="n">
         <v>130.25</v>
@@ -4220,11 +4232,11 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="1" t="n">
+      <c r="A148" s="2" t="n">
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>111.6378402709961</v>
+        <v>111.6378173828125</v>
       </c>
       <c r="C148" t="n">
         <v>134.4299926757812</v>
@@ -4249,11 +4261,11 @@
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="1" t="n">
+      <c r="A149" s="2" t="n">
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>110.9734344482422</v>
+        <v>110.9734725952148</v>
       </c>
       <c r="C149" t="n">
         <v>133.6300048828125</v>
@@ -4278,11 +4290,11 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="1" t="n">
+      <c r="A150" s="2" t="n">
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>119.1593704223633</v>
+        <v>119.1593780517578</v>
       </c>
       <c r="C150" t="n">
         <v>142.7599945068359</v>
@@ -4307,11 +4319,11 @@
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="1" t="n">
+      <c r="A151" s="2" t="n">
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>118.2579040527344</v>
+        <v>118.2578887939453</v>
       </c>
       <c r="C151" t="n">
         <v>141.6799926757812</v>
@@ -4336,7 +4348,7 @@
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="1" t="n">
+      <c r="A152" s="2" t="n">
         <v>43312</v>
       </c>
       <c r="B152" t="n">
@@ -4365,11 +4377,11 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="1" t="n">
+      <c r="A153" s="2" t="n">
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>126.3903732299805</v>
+        <v>126.3904113769531</v>
       </c>
       <c r="C153" t="n">
         <v>150.6199951171875</v>
@@ -4394,7 +4406,7 @@
       </c>
     </row>
     <row r="154">
-      <c r="A154" s="1" t="n">
+      <c r="A154" s="2" t="n">
         <v>43373</v>
       </c>
       <c r="B154" t="n">
@@ -4423,11 +4435,11 @@
       </c>
     </row>
     <row r="155">
-      <c r="A155" s="1" t="n">
+      <c r="A155" s="2" t="n">
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>122.6981964111328</v>
+        <v>122.6981887817383</v>
       </c>
       <c r="C155" t="n">
         <v>146.2200012207031</v>
@@ -4452,11 +4464,11 @@
       </c>
     </row>
     <row r="156">
-      <c r="A156" s="1" t="n">
+      <c r="A156" s="2" t="n">
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>129.7248992919922</v>
+        <v>129.7248687744141</v>
       </c>
       <c r="C156" t="n">
         <v>153.7799987792969</v>
@@ -4481,11 +4493,11 @@
       </c>
     </row>
     <row r="157">
-      <c r="A157" s="1" t="n">
+      <c r="A157" s="2" t="n">
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>116.6073379516602</v>
+        <v>116.6073226928711</v>
       </c>
       <c r="C157" t="n">
         <v>138.2299957275391</v>
@@ -4510,7 +4522,7 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="1" t="n">
+      <c r="A158" s="2" t="n">
         <v>43496</v>
       </c>
       <c r="B158" t="n">
@@ -4539,11 +4551,11 @@
       </c>
     </row>
     <row r="159">
-      <c r="A159" s="1" t="n">
+      <c r="A159" s="2" t="n">
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>142.2029266357422</v>
+        <v>142.2029571533203</v>
       </c>
       <c r="C159" t="n">
         <v>167.6999969482422</v>
@@ -4568,11 +4580,11 @@
       </c>
     </row>
     <row r="160">
-      <c r="A160" s="1" t="n">
+      <c r="A160" s="2" t="n">
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>141.7789459228516</v>
+        <v>141.7789306640625</v>
       </c>
       <c r="C160" t="n">
         <v>167.1999969482422</v>
@@ -4597,7 +4609,7 @@
       </c>
     </row>
     <row r="161">
-      <c r="A161" s="1" t="n">
+      <c r="A161" s="2" t="n">
         <v>43585</v>
       </c>
       <c r="B161" t="n">
@@ -4626,11 +4638,11 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="1" t="n">
+      <c r="A162" s="2" t="n">
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>142.1630554199219</v>
+        <v>142.1630706787109</v>
       </c>
       <c r="C162" t="n">
         <v>166.7799987792969</v>
@@ -4655,7 +4667,7 @@
       </c>
     </row>
     <row r="163">
-      <c r="A163" s="1" t="n">
+      <c r="A163" s="2" t="n">
         <v>43646</v>
       </c>
       <c r="B163" t="n">
@@ -4684,11 +4696,11 @@
       </c>
     </row>
     <row r="164">
-      <c r="A164" s="1" t="n">
+      <c r="A164" s="2" t="n">
         <v>43677</v>
       </c>
       <c r="B164" t="n">
-        <v>153.3891143798828</v>
+        <v>153.3891448974609</v>
       </c>
       <c r="C164" t="n">
         <v>179.9499969482422</v>
@@ -4713,7 +4725,7 @@
       </c>
     </row>
     <row r="165">
-      <c r="A165" s="1" t="n">
+      <c r="A165" s="2" t="n">
         <v>43708</v>
       </c>
       <c r="B165" t="n">
@@ -4742,11 +4754,11 @@
       </c>
     </row>
     <row r="166">
-      <c r="A166" s="1" t="n">
+      <c r="A166" s="2" t="n">
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>138.9222412109375</v>
+        <v>138.9222717285156</v>
       </c>
       <c r="C166" t="n">
         <v>161.9799957275391</v>
@@ -4771,11 +4783,11 @@
       </c>
     </row>
     <row r="167">
-      <c r="A167" s="1" t="n">
+      <c r="A167" s="2" t="n">
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>141.9068908691406</v>
+        <v>141.9069061279297</v>
       </c>
       <c r="C167" t="n">
         <v>165.4600067138672</v>
@@ -4800,11 +4812,11 @@
       </c>
     </row>
     <row r="168">
-      <c r="A168" s="1" t="n">
+      <c r="A168" s="2" t="n">
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>151.7646026611328</v>
+        <v>151.7646179199219</v>
       </c>
       <c r="C168" t="n">
         <v>175.9900054931641</v>
@@ -4829,7 +4841,7 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="1" t="n">
+      <c r="A169" s="2" t="n">
         <v>43830</v>
       </c>
       <c r="B169" t="n">
@@ -4858,11 +4870,11 @@
       </c>
     </row>
     <row r="170">
-      <c r="A170" s="1" t="n">
+      <c r="A170" s="2" t="n">
         <v>43861</v>
       </c>
       <c r="B170" t="n">
-        <v>154.7224578857422</v>
+        <v>154.7224426269531</v>
       </c>
       <c r="C170" t="n">
         <v>179.4199981689453</v>
@@ -4887,11 +4899,11 @@
       </c>
     </row>
     <row r="171">
-      <c r="A171" s="1" t="n">
+      <c r="A171" s="2" t="n">
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>138.6230773925781</v>
+        <v>138.6230163574219</v>
       </c>
       <c r="C171" t="n">
         <v>159.8099975585938</v>
@@ -4916,11 +4928,11 @@
       </c>
     </row>
     <row r="172">
-      <c r="A172" s="1" t="n">
+      <c r="A172" s="2" t="n">
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>122.3414611816406</v>
+        <v>122.3414535522461</v>
       </c>
       <c r="C172" t="n">
         <v>141.0399932861328</v>
@@ -4945,11 +4957,11 @@
       </c>
     </row>
     <row r="173">
-      <c r="A173" s="1" t="n">
+      <c r="A173" s="2" t="n">
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>138.6056671142578</v>
+        <v>138.6056823730469</v>
       </c>
       <c r="C173" t="n">
         <v>159.7899932861328</v>
@@ -4974,7 +4986,7 @@
       </c>
     </row>
     <row r="174">
-      <c r="A174" s="1" t="n">
+      <c r="A174" s="2" t="n">
         <v>43982</v>
       </c>
       <c r="B174" t="n">
@@ -5003,11 +5015,11 @@
       </c>
     </row>
     <row r="175">
-      <c r="A175" s="1" t="n">
+      <c r="A175" s="2" t="n">
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>147.4782867431641</v>
+        <v>147.4782562255859</v>
       </c>
       <c r="C175" t="n">
         <v>169.0700073242188</v>
@@ -5032,11 +5044,11 @@
       </c>
     </row>
     <row r="176">
-      <c r="A176" s="1" t="n">
+      <c r="A176" s="2" t="n">
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>151.2116851806641</v>
+        <v>151.2117156982422</v>
       </c>
       <c r="C176" t="n">
         <v>173.3500061035156</v>
@@ -5061,11 +5073,11 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="1" t="n">
+      <c r="A177" s="2" t="n">
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>168.7053375244141</v>
+        <v>168.7053527832031</v>
       </c>
       <c r="C177" t="n">
         <v>192.4400024414062</v>
@@ -5090,11 +5102,11 @@
       </c>
     </row>
     <row r="178">
-      <c r="A178" s="1" t="n">
+      <c r="A178" s="2" t="n">
         <v>44104</v>
       </c>
       <c r="B178" t="n">
-        <v>172.5889739990234</v>
+        <v>172.5889892578125</v>
       </c>
       <c r="C178" t="n">
         <v>196.8699951171875</v>
@@ -5119,7 +5131,7 @@
       </c>
     </row>
     <row r="179">
-      <c r="A179" s="1" t="n">
+      <c r="A179" s="2" t="n">
         <v>44135</v>
       </c>
       <c r="B179" t="n">
@@ -5148,11 +5160,11 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="1" t="n">
+      <c r="A180" s="2" t="n">
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>179.7510681152344</v>
+        <v>179.7510375976562</v>
       </c>
       <c r="C180" t="n">
         <v>204.0800018310547</v>
@@ -5177,11 +5189,11 @@
       </c>
     </row>
     <row r="181">
-      <c r="A181" s="1" t="n">
+      <c r="A181" s="2" t="n">
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>183.3975372314453</v>
+        <v>183.3974914550781</v>
       </c>
       <c r="C181" t="n">
         <v>208.2200012207031</v>
@@ -5206,11 +5218,11 @@
       </c>
     </row>
     <row r="182">
-      <c r="A182" s="1" t="n">
+      <c r="A182" s="2" t="n">
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>173.9290313720703</v>
+        <v>173.9290924072266</v>
       </c>
       <c r="C182" t="n">
         <v>197.4700012207031</v>
@@ -5235,11 +5247,11 @@
       </c>
     </row>
     <row r="183">
-      <c r="A183" s="1" t="n">
+      <c r="A183" s="2" t="n">
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>182.2441711425781</v>
+        <v>182.2441864013672</v>
       </c>
       <c r="C183" t="n">
         <v>205.9600067138672</v>
@@ -5264,7 +5276,7 @@
       </c>
     </row>
     <row r="184">
-      <c r="A184" s="1" t="n">
+      <c r="A184" s="2" t="n">
         <v>44286</v>
       </c>
       <c r="B184" t="n">
@@ -5293,11 +5305,11 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="1" t="n">
+      <c r="A185" s="2" t="n">
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>196.5168304443359</v>
+        <v>196.5167999267578</v>
       </c>
       <c r="C185" t="n">
         <v>222.0899963378906</v>
@@ -5322,11 +5334,11 @@
       </c>
     </row>
     <row r="186">
-      <c r="A186" s="1" t="n">
+      <c r="A186" s="2" t="n">
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>199.8079071044922</v>
+        <v>199.8079223632812</v>
       </c>
       <c r="C186" t="n">
         <v>224.7299957275391</v>
@@ -5351,11 +5363,11 @@
       </c>
     </row>
     <row r="187">
-      <c r="A187" s="1" t="n">
+      <c r="A187" s="2" t="n">
         <v>44377</v>
       </c>
       <c r="B187" t="n">
-        <v>195.5402374267578</v>
+        <v>195.5402069091797</v>
       </c>
       <c r="C187" t="n">
         <v>219.9299926757812</v>
@@ -5380,7 +5392,7 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="1" t="n">
+      <c r="A188" s="2" t="n">
         <v>44408</v>
       </c>
       <c r="B188" t="n">
@@ -5409,11 +5421,11 @@
       </c>
     </row>
     <row r="189">
-      <c r="A189" s="1" t="n">
+      <c r="A189" s="2" t="n">
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.7290496826172</v>
+        <v>193.72900390625</v>
       </c>
       <c r="C189" t="n">
         <v>216.8399963378906</v>
@@ -5438,11 +5450,11 @@
       </c>
     </row>
     <row r="190">
-      <c r="A190" s="1" t="n">
+      <c r="A190" s="2" t="n">
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>175.1191101074219</v>
+        <v>175.1191253662109</v>
       </c>
       <c r="C190" t="n">
         <v>196.0099945068359</v>
@@ -5467,11 +5479,11 @@
       </c>
     </row>
     <row r="191">
-      <c r="A191" s="1" t="n">
+      <c r="A191" s="2" t="n">
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>215.67138671875</v>
+        <v>215.6714019775391</v>
       </c>
       <c r="C191" t="n">
         <v>241.3999938964844</v>
@@ -5496,7 +5508,7 @@
       </c>
     </row>
     <row r="192">
-      <c r="A192" s="1" t="n">
+      <c r="A192" s="2" t="n">
         <v>44530</v>
       </c>
       <c r="B192" t="n">
@@ -5525,11 +5537,11 @@
       </c>
     </row>
     <row r="193">
-      <c r="A193" s="1" t="n">
+      <c r="A193" s="2" t="n">
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>226.1536254882812</v>
+        <v>226.1536407470703</v>
       </c>
       <c r="C193" t="n">
         <v>251.9299926757812</v>
@@ -5554,11 +5566,11 @@
       </c>
     </row>
     <row r="194">
-      <c r="A194" s="1" t="n">
+      <c r="A194" s="2" t="n">
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>219.5287170410156</v>
+        <v>219.5287933349609</v>
       </c>
       <c r="C194" t="n">
         <v>244.5500030517578</v>
@@ -5583,11 +5595,11 @@
       </c>
     </row>
     <row r="195">
-      <c r="A195" s="1" t="n">
+      <c r="A195" s="2" t="n">
         <v>44620</v>
       </c>
       <c r="B195" t="n">
-        <v>221.866943359375</v>
+        <v>221.8669128417969</v>
       </c>
       <c r="C195" t="n">
         <v>245.9499969482422</v>
@@ -5612,7 +5624,7 @@
       </c>
     </row>
     <row r="196">
-      <c r="A196" s="1" t="n">
+      <c r="A196" s="2" t="n">
         <v>44651</v>
       </c>
       <c r="B196" t="n">
@@ -5641,7 +5653,7 @@
       </c>
     </row>
     <row r="197">
-      <c r="A197" s="1" t="n">
+      <c r="A197" s="2" t="n">
         <v>44681</v>
       </c>
       <c r="B197" t="n">
@@ -5670,11 +5682,11 @@
       </c>
     </row>
     <row r="198">
-      <c r="A198" s="1" t="n">
+      <c r="A198" s="2" t="n">
         <v>44712</v>
       </c>
       <c r="B198" t="n">
-        <v>199.4310455322266</v>
+        <v>199.4310607910156</v>
       </c>
       <c r="C198" t="n">
         <v>219.7799987792969</v>
@@ -5699,7 +5711,7 @@
       </c>
     </row>
     <row r="199">
-      <c r="A199" s="1" t="n">
+      <c r="A199" s="2" t="n">
         <v>44742</v>
       </c>
       <c r="B199" t="n">
@@ -5728,7 +5740,7 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="1" t="n">
+      <c r="A200" s="2" t="n">
         <v>44773</v>
       </c>
       <c r="B200" t="n">
@@ -5757,7 +5769,7 @@
       </c>
     </row>
     <row r="201">
-      <c r="A201" s="1" t="n">
+      <c r="A201" s="2" t="n">
         <v>44804</v>
       </c>
       <c r="B201" t="n">
@@ -5786,11 +5798,11 @@
       </c>
     </row>
     <row r="202">
-      <c r="A202" s="1" t="n">
+      <c r="A202" s="2" t="n">
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>177.7764434814453</v>
+        <v>177.7764129638672</v>
       </c>
       <c r="C202" t="n">
         <v>194.8200073242188</v>
@@ -5815,11 +5827,11 @@
       </c>
     </row>
     <row r="203">
-      <c r="A203" s="1" t="n">
+      <c r="A203" s="2" t="n">
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>179.8934936523438</v>
+        <v>179.8934631347656</v>
       </c>
       <c r="C203" t="n">
         <v>197.1399993896484</v>
@@ -5844,11 +5856,11 @@
       </c>
     </row>
     <row r="204">
-      <c r="A204" s="1" t="n">
+      <c r="A204" s="2" t="n">
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>198.4084320068359</v>
+        <v>198.4084167480469</v>
       </c>
       <c r="C204" t="n">
         <v>217.4299926757812</v>
@@ -5873,11 +5885,11 @@
       </c>
     </row>
     <row r="205">
-      <c r="A205" s="1" t="n">
+      <c r="A205" s="2" t="n">
         <v>44926</v>
       </c>
       <c r="B205" t="n">
-        <v>190.118896484375</v>
+        <v>190.1189117431641</v>
       </c>
       <c r="C205" t="n">
         <v>207.0700073242188</v>
@@ -5902,11 +5914,11 @@
       </c>
     </row>
     <row r="206">
-      <c r="A206" s="1" t="n">
+      <c r="A206" s="2" t="n">
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>187.4746398925781</v>
+        <v>187.4746551513672</v>
       </c>
       <c r="C206" t="n">
         <v>204.1900024414062</v>
@@ -5931,11 +5943,11 @@
       </c>
     </row>
     <row r="207">
-      <c r="A207" s="1" t="n">
+      <c r="A207" s="2" t="n">
         <v>44985</v>
       </c>
       <c r="B207" t="n">
-        <v>191.5954437255859</v>
+        <v>191.595458984375</v>
       </c>
       <c r="C207" t="n">
         <v>207.2799987792969</v>
@@ -5960,11 +5972,11 @@
       </c>
     </row>
     <row r="208">
-      <c r="A208" s="1" t="n">
+      <c r="A208" s="2" t="n">
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>186.0309906005859</v>
+        <v>186.0309753417969</v>
       </c>
       <c r="C208" t="n">
         <v>201.2599945068359</v>
@@ -5989,7 +6001,7 @@
       </c>
     </row>
     <row r="209">
-      <c r="A209" s="1" t="n">
+      <c r="A209" s="2" t="n">
         <v>45046</v>
       </c>
       <c r="B209" t="n">
@@ -6018,7 +6030,7 @@
       </c>
     </row>
     <row r="210">
-      <c r="A210" s="1" t="n">
+      <c r="A210" s="2" t="n">
         <v>45077</v>
       </c>
       <c r="B210" t="n">
@@ -6047,11 +6059,11 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="1" t="n">
+      <c r="A211" s="2" t="n">
         <v>45107</v>
       </c>
       <c r="B211" t="n">
-        <v>190.4187164306641</v>
+        <v>190.418701171875</v>
       </c>
       <c r="C211" t="n">
         <v>204.6199951171875</v>
@@ -6076,7 +6088,7 @@
       </c>
     </row>
     <row r="212">
-      <c r="A212" s="1" t="n">
+      <c r="A212" s="2" t="n">
         <v>45138</v>
       </c>
       <c r="B212" t="n">
@@ -6105,7 +6117,7 @@
       </c>
     </row>
     <row r="213">
-      <c r="A213" s="1" t="n">
+      <c r="A213" s="2" t="n">
         <v>45169</v>
       </c>
       <c r="B213" t="n">
@@ -6134,11 +6146,11 @@
       </c>
     </row>
     <row r="214">
-      <c r="A214" s="1" t="n">
+      <c r="A214" s="2" t="n">
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>190.6063537597656</v>
+        <v>190.6063995361328</v>
       </c>
       <c r="C214" t="n">
         <v>203.6300048828125</v>
@@ -6163,7 +6175,7 @@
       </c>
     </row>
     <row r="215">
-      <c r="A215" s="1" t="n">
+      <c r="A215" s="2" t="n">
         <v>45230</v>
       </c>
       <c r="B215" t="n">
@@ -6192,11 +6204,11 @@
       </c>
     </row>
     <row r="216">
-      <c r="A216" s="1" t="n">
+      <c r="A216" s="2" t="n">
         <v>45260</v>
       </c>
       <c r="B216" t="n">
-        <v>210.8623199462891</v>
+        <v>210.8623352050781</v>
       </c>
       <c r="C216" t="n">
         <v>225.2700042724609</v>
@@ -6221,11 +6233,11 @@
       </c>
     </row>
     <row r="217">
-      <c r="A217" s="1" t="n">
+      <c r="A217" s="2" t="n">
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>231.2009429931641</v>
+        <v>231.200927734375</v>
       </c>
       <c r="C217" t="n">
         <v>245.6199951171875</v>
@@ -6250,7 +6262,7 @@
       </c>
     </row>
     <row r="218">
-      <c r="A218" s="1" t="n">
+      <c r="A218" s="2" t="n">
         <v>45322</v>
       </c>
       <c r="B218" t="n">
@@ -6279,11 +6291,11 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="1" t="n">
+      <c r="A219" s="2" t="n">
         <v>45351</v>
       </c>
       <c r="B219" t="n">
-        <v>240.0290985107422</v>
+        <v>240.0291137695312</v>
       </c>
       <c r="C219" t="n">
         <v>253.6900024414062</v>
@@ -6308,11 +6320,11 @@
       </c>
     </row>
     <row r="220">
-      <c r="A220" s="1" t="n">
+      <c r="A220" s="2" t="n">
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>232.6869812011719</v>
+        <v>232.6869659423828</v>
       </c>
       <c r="C220" t="n">
         <v>245.9299926757812</v>
@@ -6337,7 +6349,7 @@
       </c>
     </row>
     <row r="221">
-      <c r="A221" s="1" t="n">
+      <c r="A221" s="2" t="n">
         <v>45412</v>
       </c>
       <c r="B221" t="n">
@@ -6366,7 +6378,7 @@
       </c>
     </row>
     <row r="222">
-      <c r="A222" s="1" t="n">
+      <c r="A222" s="2" t="n">
         <v>45443</v>
       </c>
       <c r="B222" t="n">
@@ -6395,7 +6407,7 @@
       </c>
     </row>
     <row r="223">
-      <c r="A223" s="1" t="n">
+      <c r="A223" s="2" t="n">
         <v>45473</v>
       </c>
       <c r="B223" t="n">
@@ -6424,11 +6436,11 @@
       </c>
     </row>
     <row r="224">
-      <c r="A224" s="1" t="n">
+      <c r="A224" s="2" t="n">
         <v>45504</v>
       </c>
       <c r="B224" t="n">
-        <v>234.7753143310547</v>
+        <v>234.7752838134766</v>
       </c>
       <c r="C224" t="n">
         <v>246.7299957275391</v>
@@ -6453,11 +6465,11 @@
       </c>
     </row>
     <row r="225">
-      <c r="A225" s="1" t="n">
+      <c r="A225" s="2" t="n">
         <v>45535</v>
       </c>
       <c r="B225" t="n">
-        <v>244.9782409667969</v>
+        <v>244.9782562255859</v>
       </c>
       <c r="C225" t="n">
         <v>256.0899963378906</v>
@@ -6482,11 +6494,11 @@
       </c>
     </row>
     <row r="226">
-      <c r="A226" s="1" t="n">
+      <c r="A226" s="2" t="n">
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>235.7852478027344</v>
+        <v>235.7852325439453</v>
       </c>
       <c r="C226" t="n">
         <v>246.4799957275391</v>
@@ -6511,11 +6523,11 @@
       </c>
     </row>
     <row r="227">
-      <c r="A227" s="1" t="n">
+      <c r="A227" s="2" t="n">
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>222.0005187988281</v>
+        <v>222.0005035400391</v>
       </c>
       <c r="C227" t="n">
         <v>232.0700073242188</v>
@@ -6540,11 +6552,11 @@
       </c>
     </row>
     <row r="228">
-      <c r="A228" s="1" t="n">
+      <c r="A228" s="2" t="n">
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>234.044189453125</v>
+        <v>234.0442047119141</v>
       </c>
       <c r="C228" t="n">
         <v>244.6600036621094</v>
@@ -6569,11 +6581,11 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="1" t="n">
+      <c r="A229" s="2" t="n">
         <v>45657</v>
       </c>
       <c r="B229" t="n">
-        <v>219.4040679931641</v>
+        <v>219.4040832519531</v>
       </c>
       <c r="C229" t="n">
         <v>228.0399932861328</v>
@@ -6598,11 +6610,11 @@
       </c>
     </row>
     <row r="230">
-      <c r="A230" s="1" t="n">
+      <c r="A230" s="2" t="n">
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>238.4061431884766</v>
+        <v>238.4061279296875</v>
       </c>
       <c r="C230" t="n">
         <v>247.7899932861328</v>
@@ -6627,7 +6639,7 @@
       </c>
     </row>
     <row r="231">
-      <c r="A231" s="1" t="n">
+      <c r="A231" s="2" t="n">
         <v>45716</v>
       </c>
       <c r="B231" t="n">
@@ -6656,11 +6668,11 @@
       </c>
     </row>
     <row r="232">
-      <c r="A232" s="1" t="n">
+      <c r="A232" s="2" t="n">
         <v>45747</v>
       </c>
       <c r="B232" t="n">
-        <v>228.5431671142578</v>
+        <v>228.5431823730469</v>
       </c>
       <c r="C232" t="n">
         <v>236.2400054931641</v>
@@ -6685,7 +6697,7 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="1" t="n">
+      <c r="A233" s="2" t="n">
         <v>45777</v>
       </c>
       <c r="B233" t="n">
@@ -6714,11 +6726,11 @@
       </c>
     </row>
     <row r="234">
-      <c r="A234" s="1" t="n">
+      <c r="A234" s="2" t="n">
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>215.7374267578125</v>
+        <v>215.7374420166016</v>
       </c>
       <c r="C234" t="n">
         <v>221.6600036621094</v>
@@ -6743,7 +6755,7 @@
       </c>
     </row>
     <row r="235">
-      <c r="A235" s="1" t="n">
+      <c r="A235" s="2" t="n">
         <v>45838</v>
       </c>
       <c r="B235" t="n">
@@ -6772,11 +6784,11 @@
       </c>
     </row>
     <row r="236">
-      <c r="A236" s="1" t="n">
+      <c r="A236" s="2" t="n">
         <v>45869</v>
       </c>
       <c r="B236" t="n">
-        <v>216.0391540527344</v>
+        <v>216.0391387939453</v>
       </c>
       <c r="C236" t="n">
         <v>221.9700012207031</v>
@@ -6801,7 +6813,7 @@
       </c>
     </row>
     <row r="237">
-      <c r="A237" s="1" t="n">
+      <c r="A237" s="2" t="n">
         <v>45900</v>
       </c>
       <c r="B237" t="n">
@@ -6830,11 +6842,11 @@
       </c>
     </row>
     <row r="238">
-      <c r="A238" s="1" t="n">
+      <c r="A238" s="2" t="n">
         <v>45930</v>
       </c>
       <c r="B238" t="n">
-        <v>231.4911041259766</v>
+        <v>231.4911193847656</v>
       </c>
       <c r="C238" t="n">
         <v>236.3699951171875</v>
@@ -6859,7 +6871,7 @@
       </c>
     </row>
     <row r="239">
-      <c r="A239" s="1" t="n">
+      <c r="A239" s="2" t="n">
         <v>45961</v>
       </c>
       <c r="B239" t="n">
@@ -6888,7 +6900,7 @@
       </c>
     </row>
     <row r="240">
-      <c r="A240" s="1" t="n">
+      <c r="A240" s="2" t="n">
         <v>45991</v>
       </c>
       <c r="B240" t="n">
@@ -6917,7 +6929,7 @@
       </c>
     </row>
     <row r="241">
-      <c r="A241" s="1" t="n">
+      <c r="A241" s="2" t="n">
         <v>46022</v>
       </c>
       <c r="B241" t="n">
@@ -6946,7 +6958,7 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="1" t="n">
+      <c r="A242" s="2" t="n">
         <v>46053</v>
       </c>
       <c r="B242" t="n">
@@ -6975,7 +6987,7 @@
       </c>
     </row>
     <row r="243">
-      <c r="A243" s="1" t="n">
+      <c r="A243" s="2" t="n">
         <v>46081</v>
       </c>
       <c r="B243" t="n">
@@ -7004,7 +7016,7 @@
       </c>
     </row>
     <row r="244">
-      <c r="A244" s="1" t="n">
+      <c r="A244" s="2" t="n">
         <v>46112</v>
       </c>
       <c r="B244" t="n">
@@ -7033,11 +7045,11 @@
       </c>
     </row>
     <row r="245">
-      <c r="A245" s="1" t="n">
+      <c r="A245" s="2" t="n">
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>266.8488159179688</v>
+        <v>266.8488464355469</v>
       </c>
       <c r="C245" t="n">
         <v>269.4800109863281</v>
@@ -7062,7 +7074,7 @@
       </c>
     </row>
     <row r="246">
-      <c r="A246" s="1" t="n">
+      <c r="A246" s="2" t="n">
         <v>46173</v>
       </c>
       <c r="B246" t="n">
@@ -7091,7 +7103,7 @@
       </c>
     </row>
     <row r="247">
-      <c r="A247" s="1" t="n">
+      <c r="A247" s="2" t="n">
         <v>46203</v>
       </c>
       <c r="B247" t="n">
@@ -7120,7 +7132,7 @@
       </c>
     </row>
     <row r="248">
-      <c r="A248" s="1" t="n">
+      <c r="A248" s="2" t="n">
         <v>46234</v>
       </c>
       <c r="B248" t="n">
@@ -7149,7 +7161,7 @@
       </c>
     </row>
     <row r="249">
-      <c r="A249" s="1" t="n">
+      <c r="A249" s="2" t="n">
         <v>46265</v>
       </c>
       <c r="B249" t="n">
@@ -7178,32 +7190,32 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="1" t="n">
+      <c r="A250" s="2" t="n">
         <v>46295</v>
       </c>
       <c r="B250" t="n">
-        <v>275.5299987792969</v>
+        <v>274.0700073242188</v>
       </c>
       <c r="C250" t="n">
-        <v>275.5299987792969</v>
+        <v>274.0700073242188</v>
       </c>
       <c r="D250" t="n">
-        <v>40026200</v>
+        <v>42114100</v>
       </c>
       <c r="E250" t="n">
         <v>12.36</v>
       </c>
       <c r="F250" t="n">
-        <v>22.29207109864862</v>
+        <v>22.17394881263906</v>
       </c>
       <c r="G250" t="n">
         <v>594075498</v>
       </c>
       <c r="H250" t="n">
-        <v>163685621238.7502</v>
+        <v>162818276087.9989</v>
       </c>
       <c r="I250" t="n">
-        <v>0.06737561157588762</v>
+        <v>0.07089014803973619</v>
       </c>
     </row>
   </sheetData>
@@ -7235,75 +7247,75 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>start</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>eps_trimestral</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>origen</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>eps_ttm</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>filed_ttm</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>39539</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>39629</v>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D2" t="inlineStr">
@@ -7339,13 +7351,13 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>39630</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>39721</v>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D3" t="inlineStr">
@@ -7381,13 +7393,13 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>39814</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>39903</v>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D4" t="inlineStr">
@@ -7423,13 +7435,13 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>39904</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>39994</v>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C5" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="D5" t="inlineStr">
@@ -7465,13 +7477,13 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>39995</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40086</v>
       </c>
-      <c r="C6" s="1" t="n">
+      <c r="C6" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="D6" t="inlineStr">
@@ -7507,13 +7519,13 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40087</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40178</v>
       </c>
-      <c r="C7" s="1" t="n">
+      <c r="C7" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="D7" t="inlineStr">
@@ -7540,7 +7552,7 @@
       <c r="I7" t="n">
         <v>1.87</v>
       </c>
-      <c r="J7" s="1" t="n">
+      <c r="J7" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K7" t="n">
@@ -7553,13 +7565,13 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40179</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40268</v>
       </c>
-      <c r="C8" s="1" t="n">
+      <c r="C8" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="D8" t="inlineStr">
@@ -7586,7 +7598,7 @@
       <c r="I8" t="n">
         <v>2.015</v>
       </c>
-      <c r="J8" s="1" t="n">
+      <c r="J8" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K8" t="n">
@@ -7599,13 +7611,13 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40269</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40359</v>
       </c>
-      <c r="C9" s="1" t="n">
+      <c r="C9" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="D9" t="inlineStr">
@@ -7632,7 +7644,7 @@
       <c r="I9" t="n">
         <v>2.255</v>
       </c>
-      <c r="J9" s="1" t="n">
+      <c r="J9" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K9" t="n">
@@ -7645,13 +7657,13 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40360</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40451</v>
       </c>
-      <c r="C10" s="1" t="n">
+      <c r="C10" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="D10" t="inlineStr">
@@ -7678,7 +7690,7 @@
       <c r="I10" t="n">
         <v>2.525</v>
       </c>
-      <c r="J10" s="1" t="n">
+      <c r="J10" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K10" t="n">
@@ -7691,13 +7703,13 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40452</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40543</v>
       </c>
-      <c r="C11" s="1" t="n">
+      <c r="C11" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="D11" t="inlineStr">
@@ -7724,7 +7736,7 @@
       <c r="I11" t="n">
         <v>2.765</v>
       </c>
-      <c r="J11" s="1" t="n">
+      <c r="J11" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="K11" t="n">
@@ -7737,13 +7749,13 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40544</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40633</v>
       </c>
-      <c r="C12" s="1" t="n">
+      <c r="C12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="D12" t="inlineStr">
@@ -7770,7 +7782,7 @@
       <c r="I12" t="n">
         <v>2.905</v>
       </c>
-      <c r="J12" s="1" t="n">
+      <c r="J12" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="K12" t="n">
@@ -7783,13 +7795,13 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>40634</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>40724</v>
       </c>
-      <c r="C13" s="1" t="n">
+      <c r="C13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="D13" t="inlineStr">
@@ -7816,7 +7828,7 @@
       <c r="I13" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="1" t="n">
+      <c r="J13" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="K13" t="n">
@@ -7829,13 +7841,13 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>40725</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>40816</v>
       </c>
-      <c r="C14" s="1" t="n">
+      <c r="C14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="D14" t="inlineStr">
@@ -7862,7 +7874,7 @@
       <c r="I14" t="n">
         <v>3.145</v>
       </c>
-      <c r="J14" s="1" t="n">
+      <c r="J14" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="K14" t="n">
@@ -7875,13 +7887,13 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>40817</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>40908</v>
       </c>
-      <c r="C15" s="1" t="n">
+      <c r="C15" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="D15" t="inlineStr">
@@ -7908,7 +7920,7 @@
       <c r="I15" t="n">
         <v>3.36</v>
       </c>
-      <c r="J15" s="1" t="n">
+      <c r="J15" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="K15" t="n">
@@ -7921,13 +7933,13 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>40909</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>40999</v>
       </c>
-      <c r="C16" s="1" t="n">
+      <c r="C16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="D16" t="inlineStr">
@@ -7954,7 +7966,7 @@
       <c r="I16" t="n">
         <v>3.61</v>
       </c>
-      <c r="J16" s="1" t="n">
+      <c r="J16" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="K16" t="n">
@@ -7967,13 +7979,13 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41000</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41090</v>
       </c>
-      <c r="C17" s="1" t="n">
+      <c r="C17" s="2" t="n">
         <v>41110</v>
       </c>
       <c r="D17" t="inlineStr">
@@ -8000,7 +8012,7 @@
       <c r="I17" t="n">
         <v>3.865</v>
       </c>
-      <c r="J17" s="1" t="n">
+      <c r="J17" s="2" t="n">
         <v>41110</v>
       </c>
       <c r="K17" t="n">
@@ -8013,13 +8025,13 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41091</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41182</v>
       </c>
-      <c r="C18" s="1" t="n">
+      <c r="C18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="D18" t="inlineStr">
@@ -8046,7 +8058,7 @@
       <c r="I18" t="n">
         <v>4.035</v>
       </c>
-      <c r="J18" s="1" t="n">
+      <c r="J18" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="K18" t="n">
@@ -8059,13 +8071,13 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41183</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41274</v>
       </c>
-      <c r="C19" s="1" t="n">
+      <c r="C19" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="D19" t="inlineStr">
@@ -8092,7 +8104,7 @@
       <c r="I19" t="n">
         <v>4.135</v>
       </c>
-      <c r="J19" s="1" t="n">
+      <c r="J19" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="K19" t="n">
@@ -8105,13 +8117,13 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41275</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41364</v>
       </c>
-      <c r="C20" s="1" t="n">
+      <c r="C20" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="D20" t="inlineStr">
@@ -8138,7 +8150,7 @@
       <c r="I20" t="n">
         <v>4.255</v>
       </c>
-      <c r="J20" s="1" t="n">
+      <c r="J20" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="K20" t="n">
@@ -8151,13 +8163,13 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41365</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41455</v>
       </c>
-      <c r="C21" s="1" t="n">
+      <c r="C21" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="D21" t="inlineStr">
@@ -8184,7 +8196,7 @@
       <c r="I21" t="n">
         <v>4.39</v>
       </c>
-      <c r="J21" s="1" t="n">
+      <c r="J21" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="K21" t="n">
@@ -8197,13 +8209,13 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41456</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41547</v>
       </c>
-      <c r="C22" s="1" t="n">
+      <c r="C22" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="D22" t="inlineStr">
@@ -8230,7 +8242,7 @@
       <c r="I22" t="n">
         <v>4.535</v>
       </c>
-      <c r="J22" s="1" t="n">
+      <c r="J22" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="K22" t="n">
@@ -8243,13 +8255,13 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41548</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41639</v>
       </c>
-      <c r="C23" s="1" t="n">
+      <c r="C23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="D23" t="inlineStr">
@@ -8276,7 +8288,7 @@
       <c r="I23" t="n">
         <v>4.715</v>
       </c>
-      <c r="J23" s="1" t="n">
+      <c r="J23" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="K23" t="n">
@@ -8289,13 +8301,13 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>41640</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>41729</v>
       </c>
-      <c r="C24" s="1" t="n">
+      <c r="C24" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="D24" t="inlineStr">
@@ -8322,7 +8334,7 @@
       <c r="I24" t="n">
         <v>4.890000000000001</v>
       </c>
-      <c r="J24" s="1" t="n">
+      <c r="J24" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="K24" t="n">
@@ -8335,13 +8347,13 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>41730</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>41820</v>
       </c>
-      <c r="C25" s="1" t="n">
+      <c r="C25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="D25" t="inlineStr">
@@ -8368,7 +8380,7 @@
       <c r="I25" t="n">
         <v>5.135</v>
       </c>
-      <c r="J25" s="1" t="n">
+      <c r="J25" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="K25" t="n">
@@ -8381,13 +8393,13 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>41821</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>41912</v>
       </c>
-      <c r="C26" s="1" t="n">
+      <c r="C26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="D26" t="inlineStr">
@@ -8414,7 +8426,7 @@
       <c r="I26" t="n">
         <v>5.425</v>
       </c>
-      <c r="J26" s="1" t="n">
+      <c r="J26" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="K26" t="n">
@@ -8427,13 +8439,13 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>41913</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42004</v>
       </c>
-      <c r="C27" s="1" t="n">
+      <c r="C27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="D27" t="inlineStr">
@@ -8460,7 +8472,7 @@
       <c r="I27" t="n">
         <v>5.760000000000001</v>
       </c>
-      <c r="J27" s="1" t="n">
+      <c r="J27" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="K27" t="n">
@@ -8473,13 +8485,13 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42005</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42094</v>
       </c>
-      <c r="C28" s="1" t="n">
+      <c r="C28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="D28" t="inlineStr">
@@ -8506,7 +8518,7 @@
       <c r="I28" t="n">
         <v>5.87</v>
       </c>
-      <c r="J28" s="1" t="n">
+      <c r="J28" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="K28" t="n">
@@ -8519,13 +8531,13 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42095</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42185</v>
       </c>
-      <c r="C29" s="1" t="n">
+      <c r="C29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="D29" t="inlineStr">
@@ -8552,7 +8564,7 @@
       <c r="I29" t="n">
         <v>5.82</v>
       </c>
-      <c r="J29" s="1" t="n">
+      <c r="J29" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="K29" t="n">
@@ -8565,13 +8577,13 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42186</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42277</v>
       </c>
-      <c r="C30" s="1" t="n">
+      <c r="C30" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="D30" t="inlineStr">
@@ -8598,7 +8610,7 @@
       <c r="I30" t="n">
         <v>5.79</v>
       </c>
-      <c r="J30" s="1" t="n">
+      <c r="J30" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="K30" t="n">
@@ -8611,13 +8623,13 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42278</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42369</v>
       </c>
-      <c r="C31" s="1" t="n">
+      <c r="C31" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="D31" t="inlineStr">
@@ -8644,7 +8656,7 @@
       <c r="I31" t="n">
         <v>5.49</v>
       </c>
-      <c r="J31" s="1" t="n">
+      <c r="J31" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="K31" t="n">
@@ -8657,13 +8669,13 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42370</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42460</v>
       </c>
-      <c r="C32" s="1" t="n">
+      <c r="C32" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="D32" t="inlineStr">
@@ -8690,7 +8702,7 @@
       <c r="I32" t="n">
         <v>5.35</v>
       </c>
-      <c r="J32" s="1" t="n">
+      <c r="J32" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="K32" t="n">
@@ -8703,13 +8715,13 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42461</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42551</v>
       </c>
-      <c r="C33" s="1" t="n">
+      <c r="C33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="D33" t="inlineStr">
@@ -8736,7 +8748,7 @@
       <c r="I33" t="n">
         <v>5.14</v>
       </c>
-      <c r="J33" s="1" t="n">
+      <c r="J33" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="K33" t="n">
@@ -8749,13 +8761,13 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42552</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42643</v>
       </c>
-      <c r="C34" s="1" t="n">
+      <c r="C34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="D34" t="inlineStr">
@@ -8782,7 +8794,7 @@
       <c r="I34" t="n">
         <v>5</v>
       </c>
-      <c r="J34" s="1" t="n">
+      <c r="J34" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="K34" t="n">
@@ -8795,13 +8807,13 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>42644</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>42735</v>
       </c>
-      <c r="C35" s="1" t="n">
+      <c r="C35" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="D35" t="inlineStr">
@@ -8828,7 +8840,7 @@
       <c r="I35" t="n">
         <v>5.08</v>
       </c>
-      <c r="J35" s="1" t="n">
+      <c r="J35" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="K35" t="n">
@@ -8841,13 +8853,13 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>42736</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>42825</v>
       </c>
-      <c r="C36" s="1" t="n">
+      <c r="C36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="D36" t="inlineStr">
@@ -8874,7 +8886,7 @@
       <c r="I36" t="n">
         <v>5.24</v>
       </c>
-      <c r="J36" s="1" t="n">
+      <c r="J36" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="K36" t="n">
@@ -8887,13 +8899,13 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>42826</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>42916</v>
       </c>
-      <c r="C37" s="1" t="n">
+      <c r="C37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="D37" t="inlineStr">
@@ -8920,7 +8932,7 @@
       <c r="I37" t="n">
         <v>5.52</v>
       </c>
-      <c r="J37" s="1" t="n">
+      <c r="J37" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="K37" t="n">
@@ -8933,13 +8945,13 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>42917</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43008</v>
       </c>
-      <c r="C38" s="1" t="n">
+      <c r="C38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="D38" t="inlineStr">
@@ -8966,7 +8978,7 @@
       <c r="I38" t="n">
         <v>5.66</v>
       </c>
-      <c r="J38" s="1" t="n">
+      <c r="J38" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="K38" t="n">
@@ -8979,13 +8991,13 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43009</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43100</v>
       </c>
-      <c r="C39" s="1" t="n">
+      <c r="C39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="D39" t="inlineStr">
@@ -9012,7 +9024,7 @@
       <c r="I39" t="n">
         <v>13.52</v>
       </c>
-      <c r="J39" s="1" t="n">
+      <c r="J39" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="K39" t="n">
@@ -9025,13 +9037,13 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43101</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43190</v>
       </c>
-      <c r="C40" s="1" t="n">
+      <c r="C40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="D40" t="inlineStr">
@@ -9058,7 +9070,7 @@
       <c r="I40" t="n">
         <v>13.88</v>
       </c>
-      <c r="J40" s="1" t="n">
+      <c r="J40" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="K40" t="n">
@@ -9071,13 +9083,13 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43191</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43281</v>
       </c>
-      <c r="C41" s="1" t="n">
+      <c r="C41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="D41" t="inlineStr">
@@ -9104,7 +9116,7 @@
       <c r="I41" t="n">
         <v>14.41</v>
       </c>
-      <c r="J41" s="1" t="n">
+      <c r="J41" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="K41" t="n">
@@ -9117,13 +9129,13 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43282</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43373</v>
       </c>
-      <c r="C42" s="1" t="n">
+      <c r="C42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="D42" t="inlineStr">
@@ -9150,7 +9162,7 @@
       <c r="I42" t="n">
         <v>15.06</v>
       </c>
-      <c r="J42" s="1" t="n">
+      <c r="J42" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="K42" t="n">
@@ -9163,13 +9175,13 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43374</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43465</v>
       </c>
-      <c r="C43" s="1" t="n">
+      <c r="C43" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="D43" t="inlineStr">
@@ -9196,7 +9208,7 @@
       <c r="I43" t="n">
         <v>7.93</v>
       </c>
-      <c r="J43" s="1" t="n">
+      <c r="J43" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="K43" t="n">
@@ -9209,13 +9221,13 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43466</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43555</v>
       </c>
-      <c r="C44" s="1" t="n">
+      <c r="C44" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="D44" t="inlineStr">
@@ -9242,7 +9254,7 @@
       <c r="I44" t="n">
         <v>8.18</v>
       </c>
-      <c r="J44" s="1" t="n">
+      <c r="J44" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="K44" t="n">
@@ -9255,13 +9267,13 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43556</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43646</v>
       </c>
-      <c r="C45" s="1" t="n">
+      <c r="C45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="D45" t="inlineStr">
@@ -9288,7 +9300,7 @@
       <c r="I45" t="n">
         <v>8.42</v>
       </c>
-      <c r="J45" s="1" t="n">
+      <c r="J45" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="K45" t="n">
@@ -9301,13 +9313,13 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>43647</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>43738</v>
       </c>
-      <c r="C46" s="1" t="n">
+      <c r="C46" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="D46" t="inlineStr">
@@ -9334,7 +9346,7 @@
       <c r="I46" t="n">
         <v>8.49</v>
       </c>
-      <c r="J46" s="1" t="n">
+      <c r="J46" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="K46" t="n">
@@ -9347,13 +9359,13 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>43739</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>43830</v>
       </c>
-      <c r="C47" s="1" t="n">
+      <c r="C47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="D47" t="inlineStr">
@@ -9380,7 +9392,7 @@
       <c r="I47" t="n">
         <v>8.390000000000001</v>
       </c>
-      <c r="J47" s="1" t="n">
+      <c r="J47" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="K47" t="n">
@@ -9393,13 +9405,13 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>43831</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>43921</v>
       </c>
-      <c r="C48" s="1" t="n">
+      <c r="C48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="D48" t="inlineStr">
@@ -9426,7 +9438,7 @@
       <c r="I48" t="n">
         <v>8.610000000000001</v>
       </c>
-      <c r="J48" s="1" t="n">
+      <c r="J48" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="K48" t="n">
@@ -9439,13 +9451,13 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>43922</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44012</v>
       </c>
-      <c r="C49" s="1" t="n">
+      <c r="C49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="D49" t="inlineStr">
@@ -9472,7 +9484,7 @@
       <c r="I49" t="n">
         <v>8.06</v>
       </c>
-      <c r="J49" s="1" t="n">
+      <c r="J49" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="K49" t="n">
@@ -9485,13 +9497,13 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44013</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44104</v>
       </c>
-      <c r="C50" s="1" t="n">
+      <c r="C50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="D50" t="inlineStr">
@@ -9518,7 +9530,7 @@
       <c r="I50" t="n">
         <v>7.85</v>
       </c>
-      <c r="J50" s="1" t="n">
+      <c r="J50" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="K50" t="n">
@@ -9531,13 +9543,13 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44105</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44196</v>
       </c>
-      <c r="C51" s="1" t="n">
+      <c r="C51" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="D51" t="inlineStr">
@@ -9564,7 +9576,7 @@
       <c r="I51" t="n">
         <v>7.879999999999999</v>
       </c>
-      <c r="J51" s="1" t="n">
+      <c r="J51" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="K51" t="n">
@@ -9577,13 +9589,13 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44197</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44286</v>
       </c>
-      <c r="C52" s="1" t="n">
+      <c r="C52" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="D52" t="inlineStr">
@@ -9610,7 +9622,7 @@
       <c r="I52" t="n">
         <v>7.729999999999999</v>
       </c>
-      <c r="J52" s="1" t="n">
+      <c r="J52" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="K52" t="n">
@@ -9623,13 +9635,13 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44287</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44377</v>
       </c>
-      <c r="C53" s="1" t="n">
+      <c r="C53" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="D53" t="inlineStr">
@@ -9656,7 +9668,7 @@
       <c r="I53" t="n">
         <v>8.779999999999999</v>
       </c>
-      <c r="J53" s="1" t="n">
+      <c r="J53" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="K53" t="n">
@@ -9669,13 +9681,13 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44378</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44469</v>
       </c>
-      <c r="C54" s="1" t="n">
+      <c r="C54" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="D54" t="inlineStr">
@@ -9702,7 +9714,7 @@
       <c r="I54" t="n">
         <v>9.34</v>
       </c>
-      <c r="J54" s="1" t="n">
+      <c r="J54" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="K54" t="n">
@@ -9715,13 +9727,13 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44470</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44561</v>
       </c>
-      <c r="C55" s="1" t="n">
+      <c r="C55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="D55" t="inlineStr">
@@ -9748,7 +9760,7 @@
       <c r="I55" t="n">
         <v>9.949999999999999</v>
       </c>
-      <c r="J55" s="1" t="n">
+      <c r="J55" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="K55" t="n">
@@ -9761,13 +9773,13 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44562</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44651</v>
       </c>
-      <c r="C56" s="1" t="n">
+      <c r="C56" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="D56" t="inlineStr">
@@ -9794,7 +9806,7 @@
       <c r="I56" t="n">
         <v>10.52</v>
       </c>
-      <c r="J56" s="1" t="n">
+      <c r="J56" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="K56" t="n">
@@ -9807,13 +9819,13 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>44652</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>44742</v>
       </c>
-      <c r="C57" s="1" t="n">
+      <c r="C57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="D57" t="inlineStr">
@@ -9840,7 +9852,7 @@
       <c r="I57" t="n">
         <v>10.73</v>
       </c>
-      <c r="J57" s="1" t="n">
+      <c r="J57" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="K57" t="n">
@@ -9853,13 +9865,13 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>44743</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>44834</v>
       </c>
-      <c r="C58" s="1" t="n">
+      <c r="C58" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="D58" t="inlineStr">
@@ -9886,7 +9898,7 @@
       <c r="I58" t="n">
         <v>11.21</v>
       </c>
-      <c r="J58" s="1" t="n">
+      <c r="J58" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="K58" t="n">
@@ -9899,13 +9911,13 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>44835</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>44926</v>
       </c>
-      <c r="C59" s="1" t="n">
+      <c r="C59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="D59" t="inlineStr">
@@ -9932,7 +9944,7 @@
       <c r="I59" t="n">
         <v>11.21</v>
       </c>
-      <c r="J59" s="1" t="n">
+      <c r="J59" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="K59" t="n">
@@ -9945,13 +9957,13 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>44927</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45016</v>
       </c>
-      <c r="C60" s="1" t="n">
+      <c r="C60" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="D60" t="inlineStr">
@@ -9978,7 +9990,7 @@
       <c r="I60" t="n">
         <v>11.31</v>
       </c>
-      <c r="J60" s="1" t="n">
+      <c r="J60" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="K60" t="n">
@@ -9991,13 +10003,13 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45017</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45107</v>
       </c>
-      <c r="C61" s="1" t="n">
+      <c r="C61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="D61" t="inlineStr">
@@ -10024,7 +10036,7 @@
       <c r="I61" t="n">
         <v>10.95</v>
       </c>
-      <c r="J61" s="1" t="n">
+      <c r="J61" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="K61" t="n">
@@ -10037,13 +10049,13 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45108</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45199</v>
       </c>
-      <c r="C62" s="1" t="n">
+      <c r="C62" s="2" t="n">
         <v>45218</v>
       </c>
       <c r="D62" t="inlineStr">
@@ -10070,7 +10082,7 @@
       <c r="I62" t="n">
         <v>10.41</v>
       </c>
-      <c r="J62" s="1" t="n">
+      <c r="J62" s="2" t="n">
         <v>45218</v>
       </c>
       <c r="K62" t="n">
@@ -10083,13 +10095,13 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45200</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45291</v>
       </c>
-      <c r="C63" s="1" t="n">
+      <c r="C63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="D63" t="inlineStr">
@@ -10116,7 +10128,7 @@
       <c r="I63" t="n">
         <v>10.45</v>
       </c>
-      <c r="J63" s="1" t="n">
+      <c r="J63" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="K63" t="n">
@@ -10129,13 +10141,13 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45292</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45382</v>
       </c>
-      <c r="C64" s="1" t="n">
+      <c r="C64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="D64" t="inlineStr">
@@ -10162,7 +10174,7 @@
       <c r="I64" t="n">
         <v>10.47</v>
       </c>
-      <c r="J64" s="1" t="n">
+      <c r="J64" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="K64" t="n">
@@ -10175,13 +10187,13 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45383</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45473</v>
       </c>
-      <c r="C65" s="1" t="n">
+      <c r="C65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="D65" t="inlineStr">
@@ -10208,7 +10220,7 @@
       <c r="I65" t="n">
         <v>10.64</v>
       </c>
-      <c r="J65" s="1" t="n">
+      <c r="J65" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="K65" t="n">
@@ -10221,13 +10233,13 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45474</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45565</v>
       </c>
-      <c r="C66" s="1" t="n">
+      <c r="C66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="D66" t="inlineStr">
@@ -10254,7 +10266,7 @@
       <c r="I66" t="n">
         <v>10.88</v>
       </c>
-      <c r="J66" s="1" t="n">
+      <c r="J66" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="K66" t="n">
@@ -10267,13 +10279,13 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45566</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45657</v>
       </c>
-      <c r="C67" s="1" t="n">
+      <c r="C67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="D67" t="inlineStr">
@@ -10300,7 +10312,7 @@
       <c r="I67" t="n">
         <v>11.09</v>
       </c>
-      <c r="J67" s="1" t="n">
+      <c r="J67" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="K67" t="n">
@@ -10313,13 +10325,13 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>45658</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>45747</v>
       </c>
-      <c r="C68" s="1" t="n">
+      <c r="C68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="D68" t="inlineStr">
@@ -10346,7 +10358,7 @@
       <c r="I68" t="n">
         <v>11.1</v>
       </c>
-      <c r="J68" s="1" t="n">
+      <c r="J68" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="K68" t="n">
@@ -10359,13 +10371,13 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>45748</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>45838</v>
       </c>
-      <c r="C69" s="1" t="n">
+      <c r="C69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="D69" t="inlineStr">
@@ -10392,7 +10404,7 @@
       <c r="I69" t="n">
         <v>11.51</v>
       </c>
-      <c r="J69" s="1" t="n">
+      <c r="J69" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="K69" t="n">
@@ -10405,13 +10417,13 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>45839</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>45930</v>
       </c>
-      <c r="C70" s="1" t="n">
+      <c r="C70" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="D70" t="inlineStr">
@@ -10438,7 +10450,7 @@
       <c r="I70" t="n">
         <v>11.77</v>
       </c>
-      <c r="J70" s="1" t="n">
+      <c r="J70" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="K70" t="n">
@@ -10451,13 +10463,13 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="1" t="n">
+      <c r="A71" s="2" t="n">
         <v>45931</v>
       </c>
-      <c r="B71" s="1" t="n">
+      <c r="B71" s="2" t="n">
         <v>46022</v>
       </c>
-      <c r="C71" s="1" t="n">
+      <c r="C71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="D71" t="inlineStr">
@@ -10484,7 +10496,7 @@
       <c r="I71" t="n">
         <v>11.98</v>
       </c>
-      <c r="J71" s="1" t="n">
+      <c r="J71" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="K71" t="n">
@@ -10497,13 +10509,13 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="1" t="n">
+      <c r="A72" s="2" t="n">
         <v>46023</v>
       </c>
-      <c r="B72" s="1" t="n">
+      <c r="B72" s="2" t="n">
         <v>46112</v>
       </c>
-      <c r="C72" s="1" t="n">
+      <c r="C72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="D72" t="inlineStr">
@@ -10530,7 +10542,7 @@
       <c r="I72" t="n">
         <v>12.15</v>
       </c>
-      <c r="J72" s="1" t="n">
+      <c r="J72" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="K72" t="n">
@@ -10543,13 +10555,13 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="1" t="n">
+      <c r="A73" s="2" t="n">
         <v>46113</v>
       </c>
-      <c r="B73" s="1" t="n">
+      <c r="B73" s="2" t="n">
         <v>46203</v>
       </c>
-      <c r="C73" s="1" t="n">
+      <c r="C73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="D73" t="inlineStr">
@@ -10576,7 +10588,7 @@
       <c r="I73" t="n">
         <v>12.36</v>
       </c>
-      <c r="J73" s="1" t="n">
+      <c r="J73" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="K73" t="n">
@@ -10613,52 +10625,52 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>end</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>filed</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>acciones</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>form</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>fy</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>fp</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>tag</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>factor</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="n">
+      <c r="A2" s="2" t="n">
         <v>40011</v>
       </c>
-      <c r="B2" s="1" t="n">
+      <c r="B2" s="2" t="n">
         <v>40018</v>
       </c>
       <c r="C2" t="n">
@@ -10687,10 +10699,10 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="n">
+      <c r="A3" s="2" t="n">
         <v>40102</v>
       </c>
-      <c r="B3" s="1" t="n">
+      <c r="B3" s="2" t="n">
         <v>40108</v>
       </c>
       <c r="C3" t="n">
@@ -10719,10 +10731,10 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="n">
+      <c r="A4" s="2" t="n">
         <v>40207</v>
       </c>
-      <c r="B4" s="1" t="n">
+      <c r="B4" s="2" t="n">
         <v>40214</v>
       </c>
       <c r="C4" t="n">
@@ -10751,10 +10763,10 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="n">
+      <c r="A5" s="2" t="n">
         <v>40284</v>
       </c>
-      <c r="B5" s="1" t="n">
+      <c r="B5" s="2" t="n">
         <v>40291</v>
       </c>
       <c r="C5" t="n">
@@ -10783,10 +10795,10 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="n">
+      <c r="A6" s="2" t="n">
         <v>40375</v>
       </c>
-      <c r="B6" s="1" t="n">
+      <c r="B6" s="2" t="n">
         <v>40382</v>
       </c>
       <c r="C6" t="n">
@@ -10815,10 +10827,10 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="1" t="n">
+      <c r="A7" s="2" t="n">
         <v>40466</v>
       </c>
-      <c r="B7" s="1" t="n">
+      <c r="B7" s="2" t="n">
         <v>40473</v>
       </c>
       <c r="C7" t="n">
@@ -10847,10 +10859,10 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="n">
+      <c r="A8" s="2" t="n">
         <v>40571</v>
       </c>
-      <c r="B8" s="1" t="n">
+      <c r="B8" s="2" t="n">
         <v>40578</v>
       </c>
       <c r="C8" t="n">
@@ -10879,10 +10891,10 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="1" t="n">
+      <c r="A9" s="2" t="n">
         <v>40648</v>
       </c>
-      <c r="B9" s="1" t="n">
+      <c r="B9" s="2" t="n">
         <v>40654</v>
       </c>
       <c r="C9" t="n">
@@ -10911,10 +10923,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="1" t="n">
+      <c r="A10" s="2" t="n">
         <v>40739</v>
       </c>
-      <c r="B10" s="1" t="n">
+      <c r="B10" s="2" t="n">
         <v>40746</v>
       </c>
       <c r="C10" t="n">
@@ -10943,10 +10955,10 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="1" t="n">
+      <c r="A11" s="2" t="n">
         <v>40830</v>
       </c>
-      <c r="B11" s="1" t="n">
+      <c r="B11" s="2" t="n">
         <v>40837</v>
       </c>
       <c r="C11" t="n">
@@ -10975,10 +10987,10 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="n">
+      <c r="A12" s="2" t="n">
         <v>40935</v>
       </c>
-      <c r="B12" s="1" t="n">
+      <c r="B12" s="2" t="n">
         <v>40942</v>
       </c>
       <c r="C12" t="n">
@@ -11007,10 +11019,10 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="1" t="n">
+      <c r="A13" s="2" t="n">
         <v>41012</v>
       </c>
-      <c r="B13" s="1" t="n">
+      <c r="B13" s="2" t="n">
         <v>41018</v>
       </c>
       <c r="C13" t="n">
@@ -11039,10 +11051,10 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="1" t="n">
+      <c r="A14" s="2" t="n">
         <v>41103</v>
       </c>
-      <c r="B14" s="1" t="n">
+      <c r="B14" s="2" t="n">
         <v>41110</v>
       </c>
       <c r="C14" t="n">
@@ -11071,10 +11083,10 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="n">
+      <c r="A15" s="2" t="n">
         <v>41194</v>
       </c>
-      <c r="B15" s="1" t="n">
+      <c r="B15" s="2" t="n">
         <v>41200</v>
       </c>
       <c r="C15" t="n">
@@ -11103,10 +11115,10 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="1" t="n">
+      <c r="A16" s="2" t="n">
         <v>41306</v>
       </c>
-      <c r="B16" s="1" t="n">
+      <c r="B16" s="2" t="n">
         <v>41313</v>
       </c>
       <c r="C16" t="n">
@@ -11135,10 +11147,10 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="1" t="n">
+      <c r="A17" s="2" t="n">
         <v>41376</v>
       </c>
-      <c r="B17" s="1" t="n">
+      <c r="B17" s="2" t="n">
         <v>41382</v>
       </c>
       <c r="C17" t="n">
@@ -11167,10 +11179,10 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="1" t="n">
+      <c r="A18" s="2" t="n">
         <v>41467</v>
       </c>
-      <c r="B18" s="1" t="n">
+      <c r="B18" s="2" t="n">
         <v>41474</v>
       </c>
       <c r="C18" t="n">
@@ -11199,10 +11211,10 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="1" t="n">
+      <c r="A19" s="2" t="n">
         <v>41558</v>
       </c>
-      <c r="B19" s="1" t="n">
+      <c r="B19" s="2" t="n">
         <v>41564</v>
       </c>
       <c r="C19" t="n">
@@ -11231,10 +11243,10 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="1" t="n">
+      <c r="A20" s="2" t="n">
         <v>41670</v>
       </c>
-      <c r="B20" s="1" t="n">
+      <c r="B20" s="2" t="n">
         <v>41677</v>
       </c>
       <c r="C20" t="n">
@@ -11263,10 +11275,10 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="1" t="n">
+      <c r="A21" s="2" t="n">
         <v>41740</v>
       </c>
-      <c r="B21" s="1" t="n">
+      <c r="B21" s="2" t="n">
         <v>41746</v>
       </c>
       <c r="C21" t="n">
@@ -11295,10 +11307,10 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="1" t="n">
+      <c r="A22" s="2" t="n">
         <v>41838</v>
       </c>
-      <c r="B22" s="1" t="n">
+      <c r="B22" s="2" t="n">
         <v>41845</v>
       </c>
       <c r="C22" t="n">
@@ -11327,10 +11339,10 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="1" t="n">
+      <c r="A23" s="2" t="n">
         <v>41929</v>
       </c>
-      <c r="B23" s="1" t="n">
+      <c r="B23" s="2" t="n">
         <v>41935</v>
       </c>
       <c r="C23" t="n">
@@ -11359,10 +11371,10 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="1" t="n">
+      <c r="A24" s="2" t="n">
         <v>42034</v>
       </c>
-      <c r="B24" s="1" t="n">
+      <c r="B24" s="2" t="n">
         <v>42041</v>
       </c>
       <c r="C24" t="n">
@@ -11391,10 +11403,10 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="1" t="n">
+      <c r="A25" s="2" t="n">
         <v>42111</v>
       </c>
-      <c r="B25" s="1" t="n">
+      <c r="B25" s="2" t="n">
         <v>42117</v>
       </c>
       <c r="C25" t="n">
@@ -11423,10 +11435,10 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="1" t="n">
+      <c r="A26" s="2" t="n">
         <v>42202</v>
       </c>
-      <c r="B26" s="1" t="n">
+      <c r="B26" s="2" t="n">
         <v>42209</v>
       </c>
       <c r="C26" t="n">
@@ -11455,10 +11467,10 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="1" t="n">
+      <c r="A27" s="2" t="n">
         <v>42293</v>
       </c>
-      <c r="B27" s="1" t="n">
+      <c r="B27" s="2" t="n">
         <v>42299</v>
       </c>
       <c r="C27" t="n">
@@ -11487,10 +11499,10 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="1" t="n">
+      <c r="A28" s="2" t="n">
         <v>42398</v>
       </c>
-      <c r="B28" s="1" t="n">
+      <c r="B28" s="2" t="n">
         <v>42405</v>
       </c>
       <c r="C28" t="n">
@@ -11519,10 +11531,10 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="1" t="n">
+      <c r="A29" s="2" t="n">
         <v>42475</v>
       </c>
-      <c r="B29" s="1" t="n">
+      <c r="B29" s="2" t="n">
         <v>42481</v>
       </c>
       <c r="C29" t="n">
@@ -11551,10 +11563,10 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="1" t="n">
+      <c r="A30" s="2" t="n">
         <v>42566</v>
       </c>
-      <c r="B30" s="1" t="n">
+      <c r="B30" s="2" t="n">
         <v>42572</v>
       </c>
       <c r="C30" t="n">
@@ -11583,10 +11595,10 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="1" t="n">
+      <c r="A31" s="2" t="n">
         <v>42657</v>
       </c>
-      <c r="B31" s="1" t="n">
+      <c r="B31" s="2" t="n">
         <v>42663</v>
       </c>
       <c r="C31" t="n">
@@ -11615,10 +11627,10 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="1" t="n">
+      <c r="A32" s="2" t="n">
         <v>42762</v>
       </c>
-      <c r="B32" s="1" t="n">
+      <c r="B32" s="2" t="n">
         <v>42769</v>
       </c>
       <c r="C32" t="n">
@@ -11647,10 +11659,10 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="1" t="n">
+      <c r="A33" s="2" t="n">
         <v>42846</v>
       </c>
-      <c r="B33" s="1" t="n">
+      <c r="B33" s="2" t="n">
         <v>42852</v>
       </c>
       <c r="C33" t="n">
@@ -11679,10 +11691,10 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="1" t="n">
+      <c r="A34" s="2" t="n">
         <v>42930</v>
       </c>
-      <c r="B34" s="1" t="n">
+      <c r="B34" s="2" t="n">
         <v>42936</v>
       </c>
       <c r="C34" t="n">
@@ -11711,10 +11723,10 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="1" t="n">
+      <c r="A35" s="2" t="n">
         <v>43028</v>
       </c>
-      <c r="B35" s="1" t="n">
+      <c r="B35" s="2" t="n">
         <v>43034</v>
       </c>
       <c r="C35" t="n">
@@ -11743,10 +11755,10 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="1" t="n">
+      <c r="A36" s="2" t="n">
         <v>43133</v>
       </c>
-      <c r="B36" s="1" t="n">
+      <c r="B36" s="2" t="n">
         <v>43140</v>
       </c>
       <c r="C36" t="n">
@@ -11775,10 +11787,10 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="1" t="n">
+      <c r="A37" s="2" t="n">
         <v>43210</v>
       </c>
-      <c r="B37" s="1" t="n">
+      <c r="B37" s="2" t="n">
         <v>43216</v>
       </c>
       <c r="C37" t="n">
@@ -11807,10 +11819,10 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="1" t="n">
+      <c r="A38" s="2" t="n">
         <v>43294</v>
       </c>
-      <c r="B38" s="1" t="n">
+      <c r="B38" s="2" t="n">
         <v>43300</v>
       </c>
       <c r="C38" t="n">
@@ -11839,10 +11851,10 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="1" t="n">
+      <c r="A39" s="2" t="n">
         <v>43392</v>
       </c>
-      <c r="B39" s="1" t="n">
+      <c r="B39" s="2" t="n">
         <v>43398</v>
       </c>
       <c r="C39" t="n">
@@ -11871,10 +11883,10 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="1" t="n">
+      <c r="A40" s="2" t="n">
         <v>43497</v>
       </c>
-      <c r="B40" s="1" t="n">
+      <c r="B40" s="2" t="n">
         <v>43504</v>
       </c>
       <c r="C40" t="n">
@@ -11903,10 +11915,10 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="1" t="n">
+      <c r="A41" s="2" t="n">
         <v>43567</v>
       </c>
-      <c r="B41" s="1" t="n">
+      <c r="B41" s="2" t="n">
         <v>43573</v>
       </c>
       <c r="C41" t="n">
@@ -11935,10 +11947,10 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="1" t="n">
+      <c r="A42" s="2" t="n">
         <v>43658</v>
       </c>
-      <c r="B42" s="1" t="n">
+      <c r="B42" s="2" t="n">
         <v>43664</v>
       </c>
       <c r="C42" t="n">
@@ -11967,10 +11979,10 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="1" t="n">
+      <c r="A43" s="2" t="n">
         <v>43749</v>
       </c>
-      <c r="B43" s="1" t="n">
+      <c r="B43" s="2" t="n">
         <v>43755</v>
       </c>
       <c r="C43" t="n">
@@ -11999,10 +12011,10 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="1" t="n">
+      <c r="A44" s="2" t="n">
         <v>43861</v>
       </c>
-      <c r="B44" s="1" t="n">
+      <c r="B44" s="2" t="n">
         <v>43868</v>
       </c>
       <c r="C44" t="n">
@@ -12031,10 +12043,10 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="1" t="n">
+      <c r="A45" s="2" t="n">
         <v>43938</v>
       </c>
-      <c r="B45" s="1" t="n">
+      <c r="B45" s="2" t="n">
         <v>43944</v>
       </c>
       <c r="C45" t="n">
@@ -12063,10 +12075,10 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="1" t="n">
+      <c r="A46" s="2" t="n">
         <v>44029</v>
       </c>
-      <c r="B46" s="1" t="n">
+      <c r="B46" s="2" t="n">
         <v>44035</v>
       </c>
       <c r="C46" t="n">
@@ -12095,10 +12107,10 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="1" t="n">
+      <c r="A47" s="2" t="n">
         <v>44120</v>
       </c>
-      <c r="B47" s="1" t="n">
+      <c r="B47" s="2" t="n">
         <v>44126</v>
       </c>
       <c r="C47" t="n">
@@ -12127,10 +12139,10 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="1" t="n">
+      <c r="A48" s="2" t="n">
         <v>44225</v>
       </c>
-      <c r="B48" s="1" t="n">
+      <c r="B48" s="2" t="n">
         <v>44232</v>
       </c>
       <c r="C48" t="n">
@@ -12159,10 +12171,10 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="1" t="n">
+      <c r="A49" s="2" t="n">
         <v>44302</v>
       </c>
-      <c r="B49" s="1" t="n">
+      <c r="B49" s="2" t="n">
         <v>44308</v>
       </c>
       <c r="C49" t="n">
@@ -12191,10 +12203,10 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="1" t="n">
+      <c r="A50" s="2" t="n">
         <v>44393</v>
       </c>
-      <c r="B50" s="1" t="n">
+      <c r="B50" s="2" t="n">
         <v>44399</v>
       </c>
       <c r="C50" t="n">
@@ -12223,10 +12235,10 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="1" t="n">
+      <c r="A51" s="2" t="n">
         <v>44484</v>
       </c>
-      <c r="B51" s="1" t="n">
+      <c r="B51" s="2" t="n">
         <v>44490</v>
       </c>
       <c r="C51" t="n">
@@ -12255,10 +12267,10 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="1" t="n">
+      <c r="A52" s="2" t="n">
         <v>44589</v>
       </c>
-      <c r="B52" s="1" t="n">
+      <c r="B52" s="2" t="n">
         <v>44596</v>
       </c>
       <c r="C52" t="n">
@@ -12287,10 +12299,10 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="1" t="n">
+      <c r="A53" s="2" t="n">
         <v>44666</v>
       </c>
-      <c r="B53" s="1" t="n">
+      <c r="B53" s="2" t="n">
         <v>44672</v>
       </c>
       <c r="C53" t="n">
@@ -12319,10 +12331,10 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="1" t="n">
+      <c r="A54" s="2" t="n">
         <v>44757</v>
       </c>
-      <c r="B54" s="1" t="n">
+      <c r="B54" s="2" t="n">
         <v>44763</v>
       </c>
       <c r="C54" t="n">
@@ -12351,10 +12363,10 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="1" t="n">
+      <c r="A55" s="2" t="n">
         <v>44848</v>
       </c>
-      <c r="B55" s="1" t="n">
+      <c r="B55" s="2" t="n">
         <v>44854</v>
       </c>
       <c r="C55" t="n">
@@ -12383,10 +12395,10 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="1" t="n">
+      <c r="A56" s="2" t="n">
         <v>44960</v>
       </c>
-      <c r="B56" s="1" t="n">
+      <c r="B56" s="2" t="n">
         <v>44967</v>
       </c>
       <c r="C56" t="n">
@@ -12415,10 +12427,10 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="1" t="n">
+      <c r="A57" s="2" t="n">
         <v>45030</v>
       </c>
-      <c r="B57" s="1" t="n">
+      <c r="B57" s="2" t="n">
         <v>45036</v>
       </c>
       <c r="C57" t="n">
@@ -12447,10 +12459,10 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="1" t="n">
+      <c r="A58" s="2" t="n">
         <v>45128</v>
       </c>
-      <c r="B58" s="1" t="n">
+      <c r="B58" s="2" t="n">
         <v>45133</v>
       </c>
       <c r="C58" t="n">
@@ -12479,10 +12491,10 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="1" t="n">
+      <c r="A59" s="2" t="n">
         <v>45212</v>
       </c>
-      <c r="B59" s="1" t="n">
+      <c r="B59" s="2" t="n">
         <v>45218</v>
       </c>
       <c r="C59" t="n">
@@ -12511,10 +12523,10 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="1" t="n">
+      <c r="A60" s="2" t="n">
         <v>45324</v>
       </c>
-      <c r="B60" s="1" t="n">
+      <c r="B60" s="2" t="n">
         <v>45331</v>
       </c>
       <c r="C60" t="n">
@@ -12543,10 +12555,10 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="1" t="n">
+      <c r="A61" s="2" t="n">
         <v>45401</v>
       </c>
-      <c r="B61" s="1" t="n">
+      <c r="B61" s="2" t="n">
         <v>45407</v>
       </c>
       <c r="C61" t="n">
@@ -12575,10 +12587,10 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="1" t="n">
+      <c r="A62" s="2" t="n">
         <v>45492</v>
       </c>
-      <c r="B62" s="1" t="n">
+      <c r="B62" s="2" t="n">
         <v>45498</v>
       </c>
       <c r="C62" t="n">
@@ -12607,10 +12619,10 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="1" t="n">
+      <c r="A63" s="2" t="n">
         <v>45583</v>
       </c>
-      <c r="B63" s="1" t="n">
+      <c r="B63" s="2" t="n">
         <v>45589</v>
       </c>
       <c r="C63" t="n">
@@ -12639,10 +12651,10 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="1" t="n">
+      <c r="A64" s="2" t="n">
         <v>45688</v>
       </c>
-      <c r="B64" s="1" t="n">
+      <c r="B64" s="2" t="n">
         <v>45695</v>
       </c>
       <c r="C64" t="n">
@@ -12671,10 +12683,10 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="1" t="n">
+      <c r="A65" s="2" t="n">
         <v>45764</v>
       </c>
-      <c r="B65" s="1" t="n">
+      <c r="B65" s="2" t="n">
         <v>45771</v>
       </c>
       <c r="C65" t="n">
@@ -12703,10 +12715,10 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="1" t="n">
+      <c r="A66" s="2" t="n">
         <v>45856</v>
       </c>
-      <c r="B66" s="1" t="n">
+      <c r="B66" s="2" t="n">
         <v>45862</v>
       </c>
       <c r="C66" t="n">
@@ -12735,10 +12747,10 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="1" t="n">
+      <c r="A67" s="2" t="n">
         <v>45947</v>
       </c>
-      <c r="B67" s="1" t="n">
+      <c r="B67" s="2" t="n">
         <v>45953</v>
       </c>
       <c r="C67" t="n">
@@ -12767,10 +12779,10 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="1" t="n">
+      <c r="A68" s="2" t="n">
         <v>46052</v>
       </c>
-      <c r="B68" s="1" t="n">
+      <c r="B68" s="2" t="n">
         <v>46059</v>
       </c>
       <c r="C68" t="n">
@@ -12799,10 +12811,10 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="1" t="n">
+      <c r="A69" s="2" t="n">
         <v>46129</v>
       </c>
-      <c r="B69" s="1" t="n">
+      <c r="B69" s="2" t="n">
         <v>46135</v>
       </c>
       <c r="C69" t="n">
@@ -12831,10 +12843,10 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="1" t="n">
+      <c r="A70" s="2" t="n">
         <v>46220</v>
       </c>
-      <c r="B70" s="1" t="n">
+      <c r="B70" s="2" t="n">
         <v>46226</v>
       </c>
       <c r="C70" t="n">
@@ -12881,12 +12893,12 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>campo</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>valor</t>
         </is>

--- a/salidas/empresas/UNP.xlsx
+++ b/salidas/empresas/UNP.xlsx
@@ -498,7 +498,7 @@
         <v>38748</v>
       </c>
       <c r="B2" t="n">
-        <v>14.49657344818115</v>
+        <v>14.49657154083252</v>
       </c>
       <c r="C2" t="n">
         <v>22.11499977111816</v>
@@ -517,7 +517,7 @@
         <v>38776</v>
       </c>
       <c r="B3" t="n">
-        <v>14.51131725311279</v>
+        <v>14.51131916046143</v>
       </c>
       <c r="C3" t="n">
         <v>22.13750076293945</v>
@@ -536,7 +536,7 @@
         <v>38807</v>
       </c>
       <c r="B4" t="n">
-        <v>15.349196434021</v>
+        <v>15.34919834136963</v>
       </c>
       <c r="C4" t="n">
         <v>23.33749961853027</v>
@@ -555,7 +555,7 @@
         <v>38837</v>
       </c>
       <c r="B5" t="n">
-        <v>14.99732112884521</v>
+        <v>14.99732303619385</v>
       </c>
       <c r="C5" t="n">
         <v>22.80249977111816</v>
@@ -574,7 +574,7 @@
         <v>38868</v>
       </c>
       <c r="B6" t="n">
-        <v>15.30848026275635</v>
+        <v>15.30849075317383</v>
       </c>
       <c r="C6" t="n">
         <v>23.20000076293945</v>
@@ -593,7 +593,7 @@
         <v>38898</v>
       </c>
       <c r="B7" t="n">
-        <v>15.33487892150879</v>
+        <v>15.33488178253174</v>
       </c>
       <c r="C7" t="n">
         <v>23.23999977111816</v>
@@ -631,7 +631,7 @@
         <v>38960</v>
       </c>
       <c r="B9" t="n">
-        <v>13.30419158935547</v>
+        <v>13.30420017242432</v>
       </c>
       <c r="C9" t="n">
         <v>20.08749961853027</v>
@@ -669,7 +669,7 @@
         <v>39021</v>
       </c>
       <c r="B11" t="n">
-        <v>15.0063362121582</v>
+        <v>15.00632762908936</v>
       </c>
       <c r="C11" t="n">
         <v>22.65749931335449</v>
@@ -688,7 +688,7 @@
         <v>39051</v>
       </c>
       <c r="B12" t="n">
-        <v>15.03781414031982</v>
+        <v>15.03781604766846</v>
       </c>
       <c r="C12" t="n">
         <v>22.6299991607666</v>
@@ -707,7 +707,7 @@
         <v>39082</v>
       </c>
       <c r="B13" t="n">
-        <v>15.2870044708252</v>
+        <v>15.28700637817383</v>
       </c>
       <c r="C13" t="n">
         <v>23.0049991607666</v>
@@ -726,7 +726,7 @@
         <v>39113</v>
       </c>
       <c r="B14" t="n">
-        <v>16.7788257598877</v>
+        <v>16.77882957458496</v>
       </c>
       <c r="C14" t="n">
         <v>25.25</v>
@@ -745,7 +745,7 @@
         <v>39141</v>
       </c>
       <c r="B15" t="n">
-        <v>16.43215370178223</v>
+        <v>16.43216705322266</v>
       </c>
       <c r="C15" t="n">
         <v>24.64500045776367</v>
@@ -783,7 +783,7 @@
         <v>39202</v>
       </c>
       <c r="B17" t="n">
-        <v>19.04416847229004</v>
+        <v>19.04417419433594</v>
       </c>
       <c r="C17" t="n">
         <v>28.5625</v>
@@ -802,7 +802,7 @@
         <v>39233</v>
       </c>
       <c r="B18" t="n">
-        <v>20.17619705200195</v>
+        <v>20.17620468139648</v>
       </c>
       <c r="C18" t="n">
         <v>30.17000007629395</v>
@@ -821,7 +821,7 @@
         <v>39263</v>
       </c>
       <c r="B19" t="n">
-        <v>19.25165176391602</v>
+        <v>19.25165557861328</v>
       </c>
       <c r="C19" t="n">
         <v>28.78750038146973</v>
@@ -840,7 +840,7 @@
         <v>39294</v>
       </c>
       <c r="B20" t="n">
-        <v>19.91873359680176</v>
+        <v>19.91873931884766</v>
       </c>
       <c r="C20" t="n">
         <v>29.78499984741211</v>
@@ -859,7 +859,7 @@
         <v>39325</v>
       </c>
       <c r="B21" t="n">
-        <v>18.71293067932129</v>
+        <v>18.71293449401855</v>
       </c>
       <c r="C21" t="n">
         <v>27.89249992370605</v>
@@ -878,7 +878,7 @@
         <v>39355</v>
       </c>
       <c r="B22" t="n">
-        <v>18.96283721923828</v>
+        <v>18.96284675598145</v>
       </c>
       <c r="C22" t="n">
         <v>28.26499938964844</v>
@@ -897,7 +897,7 @@
         <v>39386</v>
       </c>
       <c r="B23" t="n">
-        <v>21.47533988952637</v>
+        <v>21.4753475189209</v>
       </c>
       <c r="C23" t="n">
         <v>32.0099983215332</v>
@@ -916,7 +916,7 @@
         <v>39416</v>
       </c>
       <c r="B24" t="n">
-        <v>21.23364448547363</v>
+        <v>21.2336483001709</v>
       </c>
       <c r="C24" t="n">
         <v>31.53499984741211</v>
@@ -935,7 +935,7 @@
         <v>39447</v>
       </c>
       <c r="B25" t="n">
-        <v>21.1461181640625</v>
+        <v>21.14611625671387</v>
       </c>
       <c r="C25" t="n">
         <v>31.40500068664551</v>
@@ -954,7 +954,7 @@
         <v>39478</v>
       </c>
       <c r="B26" t="n">
-        <v>21.0013484954834</v>
+        <v>21.00135803222656</v>
       </c>
       <c r="C26" t="n">
         <v>31.19000053405762</v>
@@ -973,7 +973,7 @@
         <v>39507</v>
       </c>
       <c r="B27" t="n">
-        <v>21.0013484954834</v>
+        <v>21.00135803222656</v>
       </c>
       <c r="C27" t="n">
         <v>31.19000053405762</v>
@@ -992,7 +992,7 @@
         <v>39538</v>
       </c>
       <c r="B28" t="n">
-        <v>21.18361663818359</v>
+        <v>21.18362236022949</v>
       </c>
       <c r="C28" t="n">
         <v>31.34499931335449</v>
@@ -1011,7 +1011,7 @@
         <v>39568</v>
       </c>
       <c r="B29" t="n">
-        <v>24.5306224822998</v>
+        <v>24.53060722351074</v>
       </c>
       <c r="C29" t="n">
         <v>36.29750061035156</v>
@@ -1030,7 +1030,7 @@
         <v>39599</v>
       </c>
       <c r="B30" t="n">
-        <v>27.81341361999512</v>
+        <v>27.81341934204102</v>
       </c>
       <c r="C30" t="n">
         <v>41.15499877929688</v>
@@ -1049,7 +1049,7 @@
         <v>39629</v>
       </c>
       <c r="B31" t="n">
-        <v>25.58285140991211</v>
+        <v>25.58285522460938</v>
       </c>
       <c r="C31" t="n">
         <v>37.75</v>
@@ -1068,7 +1068,7 @@
         <v>39660</v>
       </c>
       <c r="B32" t="n">
-        <v>27.93444633483887</v>
+        <v>27.93445205688477</v>
       </c>
       <c r="C32" t="n">
         <v>41.22000122070312</v>
@@ -1087,7 +1087,7 @@
         <v>39691</v>
       </c>
       <c r="B33" t="n">
-        <v>28.52408790588379</v>
+        <v>28.52410125732422</v>
       </c>
       <c r="C33" t="n">
         <v>41.95000076293945</v>
@@ -1106,7 +1106,7 @@
         <v>39721</v>
       </c>
       <c r="B34" t="n">
-        <v>24.19277572631836</v>
+        <v>24.19278717041016</v>
       </c>
       <c r="C34" t="n">
         <v>35.58000183105469</v>
@@ -1125,7 +1125,7 @@
         <v>39752</v>
       </c>
       <c r="B35" t="n">
-        <v>22.70028877258301</v>
+        <v>22.70027923583984</v>
       </c>
       <c r="C35" t="n">
         <v>33.3849983215332</v>
@@ -1144,7 +1144,7 @@
         <v>39782</v>
       </c>
       <c r="B36" t="n">
-        <v>17.10479545593262</v>
+        <v>17.10478973388672</v>
       </c>
       <c r="C36" t="n">
         <v>25.02000045776367</v>
@@ -1163,7 +1163,7 @@
         <v>39813</v>
       </c>
       <c r="B37" t="n">
-        <v>16.33911895751953</v>
+        <v>16.339111328125</v>
       </c>
       <c r="C37" t="n">
         <v>23.89999961853027</v>
@@ -1182,7 +1182,7 @@
         <v>39844</v>
       </c>
       <c r="B38" t="n">
-        <v>14.96840572357178</v>
+        <v>14.96840190887451</v>
       </c>
       <c r="C38" t="n">
         <v>21.89500045776367</v>
@@ -1201,7 +1201,7 @@
         <v>39872</v>
       </c>
       <c r="B39" t="n">
-        <v>12.91257858276367</v>
+        <v>12.91257667541504</v>
       </c>
       <c r="C39" t="n">
         <v>18.76000022888184</v>
@@ -1220,7 +1220,7 @@
         <v>39903</v>
       </c>
       <c r="B40" t="n">
-        <v>14.14808464050293</v>
+        <v>14.14808750152588</v>
       </c>
       <c r="C40" t="n">
         <v>20.55500030517578</v>
@@ -1239,7 +1239,7 @@
         <v>39933</v>
       </c>
       <c r="B41" t="n">
-        <v>16.91162109375</v>
+        <v>16.91161918640137</v>
       </c>
       <c r="C41" t="n">
         <v>24.56999969482422</v>
@@ -1258,7 +1258,7 @@
         <v>39964</v>
       </c>
       <c r="B42" t="n">
-        <v>17.0524845123291</v>
+        <v>17.0524787902832</v>
       </c>
       <c r="C42" t="n">
         <v>24.63500022888184</v>
@@ -1296,7 +1296,7 @@
         <v>40025</v>
       </c>
       <c r="B44" t="n">
-        <v>19.90782928466797</v>
+        <v>19.90782737731934</v>
       </c>
       <c r="C44" t="n">
         <v>28.76000022888184</v>
@@ -1321,7 +1321,7 @@
         <v>40056</v>
       </c>
       <c r="B45" t="n">
-        <v>20.79338645935059</v>
+        <v>20.79338836669922</v>
       </c>
       <c r="C45" t="n">
         <v>29.90500068664551</v>
@@ -1346,7 +1346,7 @@
         <v>40086</v>
       </c>
       <c r="B46" t="n">
-        <v>20.28580284118652</v>
+        <v>20.28580665588379</v>
       </c>
       <c r="C46" t="n">
         <v>29.17499923706055</v>
@@ -1371,7 +1371,7 @@
         <v>40117</v>
       </c>
       <c r="B47" t="n">
-        <v>19.16982460021973</v>
+        <v>19.16982841491699</v>
       </c>
       <c r="C47" t="n">
         <v>27.56999969482422</v>
@@ -1396,7 +1396,7 @@
         <v>40147</v>
       </c>
       <c r="B48" t="n">
-        <v>22.08538055419922</v>
+        <v>22.08538246154785</v>
       </c>
       <c r="C48" t="n">
         <v>31.6299991607666</v>
@@ -1421,7 +1421,7 @@
         <v>40178</v>
       </c>
       <c r="B49" t="n">
-        <v>22.30881690979004</v>
+        <v>22.30881881713867</v>
       </c>
       <c r="C49" t="n">
         <v>31.95000076293945</v>
@@ -1446,7 +1446,7 @@
         <v>40209</v>
       </c>
       <c r="B50" t="n">
-        <v>21.12180519104004</v>
+        <v>21.12180709838867</v>
       </c>
       <c r="C50" t="n">
         <v>30.25</v>
@@ -1471,7 +1471,7 @@
         <v>40237</v>
       </c>
       <c r="B51" t="n">
-        <v>23.61631202697754</v>
+        <v>23.6163158416748</v>
       </c>
       <c r="C51" t="n">
         <v>33.68500137329102</v>
@@ -1496,7 +1496,7 @@
         <v>40268</v>
       </c>
       <c r="B52" t="n">
-        <v>25.69505500793457</v>
+        <v>25.6950511932373</v>
       </c>
       <c r="C52" t="n">
         <v>36.65000152587891</v>
@@ -1521,7 +1521,7 @@
         <v>40298</v>
       </c>
       <c r="B53" t="n">
-        <v>26.52234840393066</v>
+        <v>26.52234077453613</v>
       </c>
       <c r="C53" t="n">
         <v>37.83000183105469</v>
@@ -1546,7 +1546,7 @@
         <v>40329</v>
       </c>
       <c r="B54" t="n">
-        <v>25.16061782836914</v>
+        <v>25.16061592102051</v>
       </c>
       <c r="C54" t="n">
         <v>35.71500015258789</v>
@@ -1571,7 +1571,7 @@
         <v>40359</v>
       </c>
       <c r="B55" t="n">
-        <v>24.48431777954102</v>
+        <v>24.48432540893555</v>
       </c>
       <c r="C55" t="n">
         <v>34.75500106811523</v>
@@ -1596,7 +1596,7 @@
         <v>40390</v>
       </c>
       <c r="B56" t="n">
-        <v>26.30188941955566</v>
+        <v>26.30187606811523</v>
       </c>
       <c r="C56" t="n">
         <v>37.33499908447266</v>
@@ -1621,7 +1621,7 @@
         <v>40421</v>
       </c>
       <c r="B57" t="n">
-        <v>25.81013298034668</v>
+        <v>25.81013107299805</v>
       </c>
       <c r="C57" t="n">
         <v>36.47000122070312</v>
@@ -1646,7 +1646,7 @@
         <v>40451</v>
       </c>
       <c r="B58" t="n">
-        <v>28.94528388977051</v>
+        <v>28.94527816772461</v>
       </c>
       <c r="C58" t="n">
         <v>40.90000152587891</v>
@@ -1671,7 +1671,7 @@
         <v>40482</v>
       </c>
       <c r="B59" t="n">
-        <v>31.02594184875488</v>
+        <v>31.02594375610352</v>
       </c>
       <c r="C59" t="n">
         <v>43.84000015258789</v>
@@ -1696,7 +1696,7 @@
         <v>40512</v>
       </c>
       <c r="B60" t="n">
-        <v>32.01988220214844</v>
+        <v>32.01989364624023</v>
       </c>
       <c r="C60" t="n">
         <v>45.05500030517578</v>
@@ -1721,7 +1721,7 @@
         <v>40543</v>
       </c>
       <c r="B61" t="n">
-        <v>32.92601013183594</v>
+        <v>32.9260139465332</v>
       </c>
       <c r="C61" t="n">
         <v>46.33000183105469</v>
@@ -1746,7 +1746,7 @@
         <v>40574</v>
       </c>
       <c r="B62" t="n">
-        <v>33.62602233886719</v>
+        <v>33.62604522705078</v>
       </c>
       <c r="C62" t="n">
         <v>47.31499862670898</v>
@@ -1771,7 +1771,7 @@
         <v>40602</v>
       </c>
       <c r="B63" t="n">
-        <v>34.04299545288086</v>
+        <v>34.04300689697266</v>
       </c>
       <c r="C63" t="n">
         <v>47.70500183105469</v>
@@ -1800,7 +1800,7 @@
         <v>40633</v>
       </c>
       <c r="B64" t="n">
-        <v>35.08487701416016</v>
+        <v>35.08486175537109</v>
       </c>
       <c r="C64" t="n">
         <v>49.16500091552734</v>
@@ -1829,7 +1829,7 @@
         <v>40663</v>
       </c>
       <c r="B65" t="n">
-        <v>36.91886138916016</v>
+        <v>36.91887664794922</v>
       </c>
       <c r="C65" t="n">
         <v>51.73500061035156</v>
@@ -1858,7 +1858,7 @@
         <v>40694</v>
       </c>
       <c r="B66" t="n">
-        <v>37.6283073425293</v>
+        <v>37.62830352783203</v>
       </c>
       <c r="C66" t="n">
         <v>52.48500061035156</v>
@@ -1887,7 +1887,7 @@
         <v>40724</v>
       </c>
       <c r="B67" t="n">
-        <v>37.42399215698242</v>
+        <v>37.42398071289062</v>
       </c>
       <c r="C67" t="n">
         <v>52.20000076293945</v>
@@ -1916,7 +1916,7 @@
         <v>40755</v>
       </c>
       <c r="B68" t="n">
-        <v>36.73573684692383</v>
+        <v>36.7357292175293</v>
       </c>
       <c r="C68" t="n">
         <v>51.2400016784668</v>
@@ -1945,7 +1945,7 @@
         <v>40786</v>
       </c>
       <c r="B69" t="n">
-        <v>33.21611404418945</v>
+        <v>33.21609497070312</v>
       </c>
       <c r="C69" t="n">
         <v>46.08499908447266</v>
@@ -1974,7 +1974,7 @@
         <v>40816</v>
       </c>
       <c r="B70" t="n">
-        <v>29.43213653564453</v>
+        <v>29.43214416503906</v>
       </c>
       <c r="C70" t="n">
         <v>40.83499908447266</v>
@@ -2003,7 +2003,7 @@
         <v>40847</v>
       </c>
       <c r="B71" t="n">
-        <v>35.88291549682617</v>
+        <v>35.88293075561523</v>
       </c>
       <c r="C71" t="n">
         <v>49.78499984741211</v>
@@ -2032,7 +2032,7 @@
         <v>40877</v>
       </c>
       <c r="B72" t="n">
-        <v>37.50324249267578</v>
+        <v>37.50323867797852</v>
       </c>
       <c r="C72" t="n">
         <v>51.70500183105469</v>
@@ -2061,7 +2061,7 @@
         <v>40908</v>
       </c>
       <c r="B73" t="n">
-        <v>38.42077255249023</v>
+        <v>38.42079162597656</v>
       </c>
       <c r="C73" t="n">
         <v>52.97000122070312</v>
@@ -2090,7 +2090,7 @@
         <v>40939</v>
       </c>
       <c r="B74" t="n">
-        <v>41.45629501342773</v>
+        <v>41.45629119873047</v>
       </c>
       <c r="C74" t="n">
         <v>57.15499877929688</v>
@@ -2119,7 +2119,7 @@
         <v>40968</v>
       </c>
       <c r="B75" t="n">
-        <v>40.19803237915039</v>
+        <v>40.19802093505859</v>
       </c>
       <c r="C75" t="n">
         <v>55.125</v>
@@ -2148,7 +2148,7 @@
         <v>40999</v>
       </c>
       <c r="B76" t="n">
-        <v>39.18806457519531</v>
+        <v>39.18806838989258</v>
       </c>
       <c r="C76" t="n">
         <v>53.7400016784668</v>
@@ -2177,7 +2177,7 @@
         <v>41029</v>
       </c>
       <c r="B77" t="n">
-        <v>40.99651718139648</v>
+        <v>40.99653625488281</v>
       </c>
       <c r="C77" t="n">
         <v>56.22000122070312</v>
@@ -2235,7 +2235,7 @@
         <v>41090</v>
       </c>
       <c r="B79" t="n">
-        <v>43.73594284057617</v>
+        <v>43.73592758178711</v>
       </c>
       <c r="C79" t="n">
         <v>59.65499877929688</v>
@@ -2264,7 +2264,7 @@
         <v>41121</v>
       </c>
       <c r="B80" t="n">
-        <v>44.94563674926758</v>
+        <v>44.94562911987305</v>
       </c>
       <c r="C80" t="n">
         <v>61.30500030517578</v>
@@ -2293,7 +2293,7 @@
         <v>41152</v>
       </c>
       <c r="B81" t="n">
-        <v>44.73406600952148</v>
+        <v>44.73406982421875</v>
       </c>
       <c r="C81" t="n">
         <v>60.72000122070312</v>
@@ -2322,7 +2322,7 @@
         <v>41182</v>
       </c>
       <c r="B82" t="n">
-        <v>43.72475051879883</v>
+        <v>43.72475433349609</v>
       </c>
       <c r="C82" t="n">
         <v>59.34999847412109</v>
@@ -2351,7 +2351,7 @@
         <v>41213</v>
       </c>
       <c r="B83" t="n">
-        <v>45.31975173950195</v>
+        <v>45.31974792480469</v>
       </c>
       <c r="C83" t="n">
         <v>61.51499938964844</v>
@@ -2380,7 +2380,7 @@
         <v>41243</v>
       </c>
       <c r="B84" t="n">
-        <v>45.4843864440918</v>
+        <v>45.48439788818359</v>
       </c>
       <c r="C84" t="n">
         <v>61.38999938964844</v>
@@ -2409,7 +2409,7 @@
         <v>41274</v>
       </c>
       <c r="B85" t="n">
-        <v>46.57352066040039</v>
+        <v>46.57352828979492</v>
       </c>
       <c r="C85" t="n">
         <v>62.86000061035156</v>
@@ -2467,7 +2467,7 @@
         <v>41333</v>
       </c>
       <c r="B87" t="n">
-        <v>51.05752182006836</v>
+        <v>51.05753326416016</v>
       </c>
       <c r="C87" t="n">
         <v>68.55500030517578</v>
@@ -2496,7 +2496,7 @@
         <v>41364</v>
       </c>
       <c r="B88" t="n">
-        <v>53.03116226196289</v>
+        <v>53.03116607666016</v>
       </c>
       <c r="C88" t="n">
         <v>71.20500183105469</v>
@@ -2554,7 +2554,7 @@
         <v>41425</v>
       </c>
       <c r="B90" t="n">
-        <v>57.83095169067383</v>
+        <v>57.8309326171875</v>
       </c>
       <c r="C90" t="n">
         <v>77.30999755859375</v>
@@ -2612,7 +2612,7 @@
         <v>41486</v>
       </c>
       <c r="B92" t="n">
-        <v>59.31579971313477</v>
+        <v>59.31578063964844</v>
       </c>
       <c r="C92" t="n">
         <v>79.29499816894531</v>
@@ -2641,7 +2641,7 @@
         <v>41517</v>
       </c>
       <c r="B93" t="n">
-        <v>57.72389984130859</v>
+        <v>57.72389602661133</v>
       </c>
       <c r="C93" t="n">
         <v>76.76999664306641</v>
@@ -2670,7 +2670,7 @@
         <v>41547</v>
       </c>
       <c r="B94" t="n">
-        <v>58.40061569213867</v>
+        <v>58.40059661865234</v>
       </c>
       <c r="C94" t="n">
         <v>77.66999816894531</v>
@@ -2699,7 +2699,7 @@
         <v>41578</v>
       </c>
       <c r="B95" t="n">
-        <v>56.91934967041016</v>
+        <v>56.91936111450195</v>
       </c>
       <c r="C95" t="n">
         <v>75.69999694824219</v>
@@ -2728,7 +2728,7 @@
         <v>41608</v>
       </c>
       <c r="B96" t="n">
-        <v>61.21649551391602</v>
+        <v>61.21649932861328</v>
       </c>
       <c r="C96" t="n">
         <v>81.01999664306641</v>
@@ -2757,7 +2757,7 @@
         <v>41639</v>
       </c>
       <c r="B97" t="n">
-        <v>63.46810531616211</v>
+        <v>63.46809768676758</v>
       </c>
       <c r="C97" t="n">
         <v>84</v>
@@ -2786,7 +2786,7 @@
         <v>41670</v>
       </c>
       <c r="B98" t="n">
-        <v>65.82549285888672</v>
+        <v>65.82548522949219</v>
       </c>
       <c r="C98" t="n">
         <v>87.12000274658203</v>
@@ -2815,7 +2815,7 @@
         <v>41698</v>
       </c>
       <c r="B99" t="n">
-        <v>68.49392700195312</v>
+        <v>68.49390411376953</v>
       </c>
       <c r="C99" t="n">
         <v>90.19000244140625</v>
@@ -2844,7 +2844,7 @@
         <v>41729</v>
       </c>
       <c r="B100" t="n">
-        <v>71.25825500488281</v>
+        <v>71.25824737548828</v>
       </c>
       <c r="C100" t="n">
         <v>93.83000183105469</v>
@@ -2873,7 +2873,7 @@
         <v>41759</v>
       </c>
       <c r="B101" t="n">
-        <v>72.31005096435547</v>
+        <v>72.31008148193359</v>
       </c>
       <c r="C101" t="n">
         <v>95.21499633789062</v>
@@ -2902,7 +2902,7 @@
         <v>41790</v>
       </c>
       <c r="B102" t="n">
-        <v>75.66680908203125</v>
+        <v>75.66680145263672</v>
       </c>
       <c r="C102" t="n">
         <v>99.63500213623047</v>
@@ -2931,7 +2931,7 @@
         <v>41820</v>
       </c>
       <c r="B103" t="n">
-        <v>76.09297943115234</v>
+        <v>76.09297180175781</v>
       </c>
       <c r="C103" t="n">
         <v>99.75</v>
@@ -2960,7 +2960,7 @@
         <v>41851</v>
       </c>
       <c r="B104" t="n">
-        <v>74.99449920654297</v>
+        <v>74.9945068359375</v>
       </c>
       <c r="C104" t="n">
         <v>98.30999755859375</v>
@@ -2989,7 +2989,7 @@
         <v>41882</v>
       </c>
       <c r="B105" t="n">
-        <v>80.68600463867188</v>
+        <v>80.68601226806641</v>
       </c>
       <c r="C105" t="n">
         <v>105.2699966430664</v>
@@ -3047,7 +3047,7 @@
         <v>41943</v>
       </c>
       <c r="B107" t="n">
-        <v>89.255126953125</v>
+        <v>89.25511932373047</v>
       </c>
       <c r="C107" t="n">
         <v>116.4499969482422</v>
@@ -3076,7 +3076,7 @@
         <v>41973</v>
       </c>
       <c r="B108" t="n">
-        <v>89.86479187011719</v>
+        <v>89.86476135253906</v>
       </c>
       <c r="C108" t="n">
         <v>116.7699966430664</v>
@@ -3134,7 +3134,7 @@
         <v>42035</v>
       </c>
       <c r="B110" t="n">
-        <v>90.20339202880859</v>
+        <v>90.20340728759766</v>
       </c>
       <c r="C110" t="n">
         <v>117.2099990844727</v>
@@ -3163,7 +3163,7 @@
         <v>42063</v>
       </c>
       <c r="B111" t="n">
-        <v>92.96739959716797</v>
+        <v>92.96738433837891</v>
       </c>
       <c r="C111" t="n">
         <v>120.2600021362305</v>
@@ -3192,7 +3192,7 @@
         <v>42094</v>
       </c>
       <c r="B112" t="n">
-        <v>83.72939300537109</v>
+        <v>83.72937774658203</v>
       </c>
       <c r="C112" t="n">
         <v>108.3099975585938</v>
@@ -3279,7 +3279,7 @@
         <v>42185</v>
       </c>
       <c r="B115" t="n">
-        <v>74.12226867675781</v>
+        <v>74.12226104736328</v>
       </c>
       <c r="C115" t="n">
         <v>95.37000274658203</v>
@@ -3308,7 +3308,7 @@
         <v>42216</v>
       </c>
       <c r="B116" t="n">
-        <v>75.84769439697266</v>
+        <v>75.84768676757812</v>
       </c>
       <c r="C116" t="n">
         <v>97.58999633789062</v>
@@ -3337,7 +3337,7 @@
         <v>42247</v>
       </c>
       <c r="B117" t="n">
-        <v>67.07646179199219</v>
+        <v>67.07640075683594</v>
       </c>
       <c r="C117" t="n">
         <v>85.73999786376953</v>
@@ -3366,7 +3366,7 @@
         <v>42277</v>
       </c>
       <c r="B118" t="n">
-        <v>69.16525268554688</v>
+        <v>69.16524505615234</v>
       </c>
       <c r="C118" t="n">
         <v>88.41000366210938</v>
@@ -3395,7 +3395,7 @@
         <v>42308</v>
       </c>
       <c r="B119" t="n">
-        <v>69.90065002441406</v>
+        <v>69.90064239501953</v>
       </c>
       <c r="C119" t="n">
         <v>89.34999847412109</v>
@@ -3424,7 +3424,7 @@
         <v>42338</v>
       </c>
       <c r="B120" t="n">
-        <v>66.10480499267578</v>
+        <v>66.10479736328125</v>
       </c>
       <c r="C120" t="n">
         <v>83.94999694824219</v>
@@ -3453,7 +3453,7 @@
         <v>42369</v>
       </c>
       <c r="B121" t="n">
-        <v>61.57709503173828</v>
+        <v>61.57709121704102</v>
       </c>
       <c r="C121" t="n">
         <v>78.19999694824219</v>
@@ -3482,7 +3482,7 @@
         <v>42400</v>
       </c>
       <c r="B122" t="n">
-        <v>56.69500732421875</v>
+        <v>56.69502639770508</v>
       </c>
       <c r="C122" t="n">
         <v>72</v>
@@ -3511,7 +3511,7 @@
         <v>42429</v>
       </c>
       <c r="B123" t="n">
-        <v>62.52619552612305</v>
+        <v>62.52615737915039</v>
       </c>
       <c r="C123" t="n">
         <v>78.86000061035156</v>
@@ -3540,7 +3540,7 @@
         <v>42460</v>
       </c>
       <c r="B124" t="n">
-        <v>63.07326507568359</v>
+        <v>63.07327270507812</v>
       </c>
       <c r="C124" t="n">
         <v>79.55000305175781</v>
@@ -3627,7 +3627,7 @@
         <v>42551</v>
       </c>
       <c r="B127" t="n">
-        <v>69.64038848876953</v>
+        <v>69.64041137695312</v>
       </c>
       <c r="C127" t="n">
         <v>87.25</v>
@@ -3656,7 +3656,7 @@
         <v>42582</v>
       </c>
       <c r="B128" t="n">
-        <v>74.26976013183594</v>
+        <v>74.26979064941406</v>
       </c>
       <c r="C128" t="n">
         <v>93.05000305175781</v>
@@ -3685,7 +3685,7 @@
         <v>42613</v>
       </c>
       <c r="B129" t="n">
-        <v>76.69265747070312</v>
+        <v>76.69269561767578</v>
       </c>
       <c r="C129" t="n">
         <v>95.52999877929688</v>
@@ -3714,7 +3714,7 @@
         <v>42643</v>
       </c>
       <c r="B130" t="n">
-        <v>78.29831695556641</v>
+        <v>78.29832458496094</v>
       </c>
       <c r="C130" t="n">
         <v>97.52999877929688</v>
@@ -3743,7 +3743,7 @@
         <v>42674</v>
       </c>
       <c r="B131" t="n">
-        <v>70.7919921875</v>
+        <v>70.79203796386719</v>
       </c>
       <c r="C131" t="n">
         <v>88.18000030517578</v>
@@ -3772,7 +3772,7 @@
         <v>42704</v>
       </c>
       <c r="B132" t="n">
-        <v>81.83391571044922</v>
+        <v>81.83387756347656</v>
       </c>
       <c r="C132" t="n">
         <v>101.3300018310547</v>
@@ -3801,7 +3801,7 @@
         <v>42735</v>
       </c>
       <c r="B133" t="n">
-        <v>83.73176574707031</v>
+        <v>83.73177337646484</v>
       </c>
       <c r="C133" t="n">
         <v>103.6800003051758</v>
@@ -3830,7 +3830,7 @@
         <v>42766</v>
       </c>
       <c r="B134" t="n">
-        <v>86.07381439208984</v>
+        <v>86.07379913330078</v>
       </c>
       <c r="C134" t="n">
         <v>106.5800018310547</v>
@@ -3859,7 +3859,7 @@
         <v>42794</v>
       </c>
       <c r="B135" t="n">
-        <v>87.66921997070312</v>
+        <v>87.66923522949219</v>
       </c>
       <c r="C135" t="n">
         <v>107.9400024414062</v>
@@ -3917,7 +3917,7 @@
         <v>42855</v>
       </c>
       <c r="B137" t="n">
-        <v>90.93428802490234</v>
+        <v>90.93429565429688</v>
       </c>
       <c r="C137" t="n">
         <v>111.9599990844727</v>
@@ -3946,7 +3946,7 @@
         <v>42886</v>
       </c>
       <c r="B138" t="n">
-        <v>90.08285522460938</v>
+        <v>90.08286285400391</v>
       </c>
       <c r="C138" t="n">
         <v>110.3000030517578</v>
@@ -4004,7 +4004,7 @@
         <v>42947</v>
       </c>
       <c r="B140" t="n">
-        <v>84.08824157714844</v>
+        <v>84.08820343017578</v>
       </c>
       <c r="C140" t="n">
         <v>102.9599990844727</v>
@@ -4033,7 +4033,7 @@
         <v>42978</v>
       </c>
       <c r="B141" t="n">
-        <v>86.4998779296875</v>
+        <v>86.49984741210938</v>
       </c>
       <c r="C141" t="n">
         <v>105.3000030517578</v>
@@ -4062,7 +4062,7 @@
         <v>43008</v>
       </c>
       <c r="B142" t="n">
-        <v>95.26486206054688</v>
+        <v>95.26484680175781</v>
       </c>
       <c r="C142" t="n">
         <v>115.9700012207031</v>
@@ -4091,7 +4091,7 @@
         <v>43039</v>
       </c>
       <c r="B143" t="n">
-        <v>95.11698150634766</v>
+        <v>95.11700439453125</v>
       </c>
       <c r="C143" t="n">
         <v>115.7900009155273</v>
@@ -4149,7 +4149,7 @@
         <v>43100</v>
       </c>
       <c r="B145" t="n">
-        <v>110.7780380249023</v>
+        <v>110.7780303955078</v>
       </c>
       <c r="C145" t="n">
         <v>134.1000061035156</v>
@@ -4207,7 +4207,7 @@
         <v>43159</v>
       </c>
       <c r="B147" t="n">
-        <v>108.1665496826172</v>
+        <v>108.1665267944336</v>
       </c>
       <c r="C147" t="n">
         <v>130.25</v>
@@ -4236,7 +4236,7 @@
         <v>43190</v>
       </c>
       <c r="B148" t="n">
-        <v>111.6378173828125</v>
+        <v>111.6378479003906</v>
       </c>
       <c r="C148" t="n">
         <v>134.4299926757812</v>
@@ -4265,7 +4265,7 @@
         <v>43220</v>
       </c>
       <c r="B149" t="n">
-        <v>110.9734725952148</v>
+        <v>110.9734802246094</v>
       </c>
       <c r="C149" t="n">
         <v>133.6300048828125</v>
@@ -4294,7 +4294,7 @@
         <v>43251</v>
       </c>
       <c r="B150" t="n">
-        <v>119.1593780517578</v>
+        <v>119.1593551635742</v>
       </c>
       <c r="C150" t="n">
         <v>142.7599945068359</v>
@@ -4323,7 +4323,7 @@
         <v>43281</v>
       </c>
       <c r="B151" t="n">
-        <v>118.2578887939453</v>
+        <v>118.2579345703125</v>
       </c>
       <c r="C151" t="n">
         <v>141.6799926757812</v>
@@ -4352,7 +4352,7 @@
         <v>43312</v>
       </c>
       <c r="B152" t="n">
-        <v>125.1106414794922</v>
+        <v>125.1106262207031</v>
       </c>
       <c r="C152" t="n">
         <v>149.8899993896484</v>
@@ -4381,7 +4381,7 @@
         <v>43343</v>
       </c>
       <c r="B153" t="n">
-        <v>126.3904113769531</v>
+        <v>126.3903961181641</v>
       </c>
       <c r="C153" t="n">
         <v>150.6199951171875</v>
@@ -4439,7 +4439,7 @@
         <v>43404</v>
       </c>
       <c r="B155" t="n">
-        <v>122.6981887817383</v>
+        <v>122.6982192993164</v>
       </c>
       <c r="C155" t="n">
         <v>146.2200012207031</v>
@@ -4468,7 +4468,7 @@
         <v>43434</v>
       </c>
       <c r="B156" t="n">
-        <v>129.7248687744141</v>
+        <v>129.7249298095703</v>
       </c>
       <c r="C156" t="n">
         <v>153.7799987792969</v>
@@ -4497,7 +4497,7 @@
         <v>43465</v>
       </c>
       <c r="B157" t="n">
-        <v>116.6073226928711</v>
+        <v>116.6073379516602</v>
       </c>
       <c r="C157" t="n">
         <v>138.2299957275391</v>
@@ -4526,7 +4526,7 @@
         <v>43496</v>
       </c>
       <c r="B158" t="n">
-        <v>134.1874237060547</v>
+        <v>134.1874542236328</v>
       </c>
       <c r="C158" t="n">
         <v>159.0700073242188</v>
@@ -4555,7 +4555,7 @@
         <v>43524</v>
       </c>
       <c r="B159" t="n">
-        <v>142.2029571533203</v>
+        <v>142.2029266357422</v>
       </c>
       <c r="C159" t="n">
         <v>167.6999969482422</v>
@@ -4584,7 +4584,7 @@
         <v>43555</v>
       </c>
       <c r="B160" t="n">
-        <v>141.7789306640625</v>
+        <v>141.7789459228516</v>
       </c>
       <c r="C160" t="n">
         <v>167.1999969482422</v>
@@ -4613,7 +4613,7 @@
         <v>43585</v>
       </c>
       <c r="B161" t="n">
-        <v>150.1228637695312</v>
+        <v>150.1229095458984</v>
       </c>
       <c r="C161" t="n">
         <v>177.0399932861328</v>
@@ -4642,7 +4642,7 @@
         <v>43616</v>
       </c>
       <c r="B162" t="n">
-        <v>142.1630706787109</v>
+        <v>142.1630401611328</v>
       </c>
       <c r="C162" t="n">
         <v>166.7799987792969</v>
@@ -4671,7 +4671,7 @@
         <v>43646</v>
       </c>
       <c r="B163" t="n">
-        <v>144.149169921875</v>
+        <v>144.1491546630859</v>
       </c>
       <c r="C163" t="n">
         <v>169.1100006103516</v>
@@ -4729,7 +4729,7 @@
         <v>43708</v>
       </c>
       <c r="B165" t="n">
-        <v>138.9051055908203</v>
+        <v>138.9051208496094</v>
       </c>
       <c r="C165" t="n">
         <v>161.9600067138672</v>
@@ -4758,7 +4758,7 @@
         <v>43738</v>
       </c>
       <c r="B166" t="n">
-        <v>138.9222717285156</v>
+        <v>138.9223022460938</v>
       </c>
       <c r="C166" t="n">
         <v>161.9799957275391</v>
@@ -4787,7 +4787,7 @@
         <v>43769</v>
       </c>
       <c r="B167" t="n">
-        <v>141.9069061279297</v>
+        <v>141.9069366455078</v>
       </c>
       <c r="C167" t="n">
         <v>165.4600067138672</v>
@@ -4816,7 +4816,7 @@
         <v>43799</v>
       </c>
       <c r="B168" t="n">
-        <v>151.7646179199219</v>
+        <v>151.7645721435547</v>
       </c>
       <c r="C168" t="n">
         <v>175.9900054931641</v>
@@ -4845,7 +4845,7 @@
         <v>43830</v>
       </c>
       <c r="B169" t="n">
-        <v>155.9038696289062</v>
+        <v>155.9038238525391</v>
       </c>
       <c r="C169" t="n">
         <v>180.7899932861328</v>
@@ -4903,7 +4903,7 @@
         <v>43890</v>
       </c>
       <c r="B171" t="n">
-        <v>138.6230163574219</v>
+        <v>138.6230621337891</v>
       </c>
       <c r="C171" t="n">
         <v>159.8099975585938</v>
@@ -4932,7 +4932,7 @@
         <v>43921</v>
       </c>
       <c r="B172" t="n">
-        <v>122.3414535522461</v>
+        <v>122.3414993286133</v>
       </c>
       <c r="C172" t="n">
         <v>141.0399932861328</v>
@@ -4961,7 +4961,7 @@
         <v>43951</v>
       </c>
       <c r="B173" t="n">
-        <v>138.6056823730469</v>
+        <v>138.6056671142578</v>
       </c>
       <c r="C173" t="n">
         <v>159.7899932861328</v>
@@ -4990,7 +4990,7 @@
         <v>43982</v>
       </c>
       <c r="B174" t="n">
-        <v>148.1674194335938</v>
+        <v>148.1674346923828</v>
       </c>
       <c r="C174" t="n">
         <v>169.8600006103516</v>
@@ -5019,7 +5019,7 @@
         <v>44012</v>
       </c>
       <c r="B175" t="n">
-        <v>147.4782562255859</v>
+        <v>147.4783172607422</v>
       </c>
       <c r="C175" t="n">
         <v>169.0700073242188</v>
@@ -5048,7 +5048,7 @@
         <v>44043</v>
       </c>
       <c r="B176" t="n">
-        <v>151.2117156982422</v>
+        <v>151.2116851806641</v>
       </c>
       <c r="C176" t="n">
         <v>173.3500061035156</v>
@@ -5077,7 +5077,7 @@
         <v>44074</v>
       </c>
       <c r="B177" t="n">
-        <v>168.7053527832031</v>
+        <v>168.7053833007812</v>
       </c>
       <c r="C177" t="n">
         <v>192.4400024414062</v>
@@ -5135,7 +5135,7 @@
         <v>44135</v>
       </c>
       <c r="B179" t="n">
-        <v>155.3362121582031</v>
+        <v>155.3361968994141</v>
       </c>
       <c r="C179" t="n">
         <v>177.1900024414062</v>
@@ -5164,7 +5164,7 @@
         <v>44165</v>
       </c>
       <c r="B180" t="n">
-        <v>179.7510375976562</v>
+        <v>179.7510986328125</v>
       </c>
       <c r="C180" t="n">
         <v>204.0800018310547</v>
@@ -5193,7 +5193,7 @@
         <v>44196</v>
       </c>
       <c r="B181" t="n">
-        <v>183.3974914550781</v>
+        <v>183.3975067138672</v>
       </c>
       <c r="C181" t="n">
         <v>208.2200012207031</v>
@@ -5222,7 +5222,7 @@
         <v>44227</v>
       </c>
       <c r="B182" t="n">
-        <v>173.9290924072266</v>
+        <v>173.9290313720703</v>
       </c>
       <c r="C182" t="n">
         <v>197.4700012207031</v>
@@ -5251,7 +5251,7 @@
         <v>44255</v>
       </c>
       <c r="B183" t="n">
-        <v>182.2441864013672</v>
+        <v>182.2441711425781</v>
       </c>
       <c r="C183" t="n">
         <v>205.9600067138672</v>
@@ -5280,7 +5280,7 @@
         <v>44286</v>
       </c>
       <c r="B184" t="n">
-        <v>195.0302886962891</v>
+        <v>195.0302581787109</v>
       </c>
       <c r="C184" t="n">
         <v>220.4100036621094</v>
@@ -5309,7 +5309,7 @@
         <v>44316</v>
       </c>
       <c r="B185" t="n">
-        <v>196.5167999267578</v>
+        <v>196.5168151855469</v>
       </c>
       <c r="C185" t="n">
         <v>222.0899963378906</v>
@@ -5338,7 +5338,7 @@
         <v>44347</v>
       </c>
       <c r="B186" t="n">
-        <v>199.8079223632812</v>
+        <v>199.8079376220703</v>
       </c>
       <c r="C186" t="n">
         <v>224.7299957275391</v>
@@ -5396,7 +5396,7 @@
         <v>44408</v>
       </c>
       <c r="B188" t="n">
-        <v>194.4999542236328</v>
+        <v>194.4999847412109</v>
       </c>
       <c r="C188" t="n">
         <v>218.7599945068359</v>
@@ -5425,7 +5425,7 @@
         <v>44439</v>
       </c>
       <c r="B189" t="n">
-        <v>193.72900390625</v>
+        <v>193.7290191650391</v>
       </c>
       <c r="C189" t="n">
         <v>216.8399963378906</v>
@@ -5454,7 +5454,7 @@
         <v>44469</v>
       </c>
       <c r="B190" t="n">
-        <v>175.1191253662109</v>
+        <v>175.1191101074219</v>
       </c>
       <c r="C190" t="n">
         <v>196.0099945068359</v>
@@ -5483,7 +5483,7 @@
         <v>44500</v>
       </c>
       <c r="B191" t="n">
-        <v>215.6714019775391</v>
+        <v>215.67138671875</v>
       </c>
       <c r="C191" t="n">
         <v>241.3999938964844</v>
@@ -5512,7 +5512,7 @@
         <v>44530</v>
       </c>
       <c r="B192" t="n">
-        <v>210.5252990722656</v>
+        <v>210.5253295898438</v>
       </c>
       <c r="C192" t="n">
         <v>235.6399993896484</v>
@@ -5541,7 +5541,7 @@
         <v>44561</v>
       </c>
       <c r="B193" t="n">
-        <v>226.1536407470703</v>
+        <v>226.1536560058594</v>
       </c>
       <c r="C193" t="n">
         <v>251.9299926757812</v>
@@ -5570,7 +5570,7 @@
         <v>44592</v>
       </c>
       <c r="B194" t="n">
-        <v>219.5287933349609</v>
+        <v>219.5287628173828</v>
       </c>
       <c r="C194" t="n">
         <v>244.5500030517578</v>
@@ -5628,7 +5628,7 @@
         <v>44651</v>
       </c>
       <c r="B196" t="n">
-        <v>246.4576873779297</v>
+        <v>246.4577178955078</v>
       </c>
       <c r="C196" t="n">
         <v>273.2099914550781</v>
@@ -5657,7 +5657,7 @@
         <v>44681</v>
       </c>
       <c r="B197" t="n">
-        <v>211.3486633300781</v>
+        <v>211.3486328125</v>
       </c>
       <c r="C197" t="n">
         <v>234.2899932861328</v>
@@ -5744,7 +5744,7 @@
         <v>44773</v>
       </c>
       <c r="B200" t="n">
-        <v>206.2547760009766</v>
+        <v>206.2548217773438</v>
       </c>
       <c r="C200" t="n">
         <v>227.3000030517578</v>
@@ -5773,7 +5773,7 @@
         <v>44804</v>
       </c>
       <c r="B201" t="n">
-        <v>204.8690643310547</v>
+        <v>204.8690795898438</v>
       </c>
       <c r="C201" t="n">
         <v>224.5099945068359</v>
@@ -5802,7 +5802,7 @@
         <v>44834</v>
       </c>
       <c r="B202" t="n">
-        <v>177.7764129638672</v>
+        <v>177.7764434814453</v>
       </c>
       <c r="C202" t="n">
         <v>194.8200073242188</v>
@@ -5831,7 +5831,7 @@
         <v>44865</v>
       </c>
       <c r="B203" t="n">
-        <v>179.8934631347656</v>
+        <v>179.8934783935547</v>
       </c>
       <c r="C203" t="n">
         <v>197.1399993896484</v>
@@ -5860,7 +5860,7 @@
         <v>44895</v>
       </c>
       <c r="B204" t="n">
-        <v>198.4084167480469</v>
+        <v>198.408447265625</v>
       </c>
       <c r="C204" t="n">
         <v>217.4299926757812</v>
@@ -5918,7 +5918,7 @@
         <v>44957</v>
       </c>
       <c r="B206" t="n">
-        <v>187.4746551513672</v>
+        <v>187.4746398925781</v>
       </c>
       <c r="C206" t="n">
         <v>204.1900024414062</v>
@@ -5976,7 +5976,7 @@
         <v>45016</v>
       </c>
       <c r="B208" t="n">
-        <v>186.0309753417969</v>
+        <v>186.0309906005859</v>
       </c>
       <c r="C208" t="n">
         <v>201.2599945068359</v>
@@ -6005,7 +6005,7 @@
         <v>45046</v>
       </c>
       <c r="B209" t="n">
-        <v>180.8916778564453</v>
+        <v>180.8916931152344</v>
       </c>
       <c r="C209" t="n">
         <v>195.6999969482422</v>
@@ -6034,7 +6034,7 @@
         <v>45077</v>
       </c>
       <c r="B210" t="n">
-        <v>179.1584777832031</v>
+        <v>179.1584625244141</v>
       </c>
       <c r="C210" t="n">
         <v>192.5200042724609</v>
@@ -6121,7 +6121,7 @@
         <v>45169</v>
       </c>
       <c r="B213" t="n">
-        <v>206.4629364013672</v>
+        <v>206.4629516601562</v>
       </c>
       <c r="C213" t="n">
         <v>220.5700073242188</v>
@@ -6150,7 +6150,7 @@
         <v>45199</v>
       </c>
       <c r="B214" t="n">
-        <v>190.6063995361328</v>
+        <v>190.6063690185547</v>
       </c>
       <c r="C214" t="n">
         <v>203.6300048828125</v>
@@ -6179,7 +6179,7 @@
         <v>45230</v>
       </c>
       <c r="B215" t="n">
-        <v>194.3318328857422</v>
+        <v>194.3318176269531</v>
       </c>
       <c r="C215" t="n">
         <v>207.6100006103516</v>
@@ -6237,7 +6237,7 @@
         <v>45291</v>
       </c>
       <c r="B217" t="n">
-        <v>231.200927734375</v>
+        <v>231.2009124755859</v>
       </c>
       <c r="C217" t="n">
         <v>245.6199951171875</v>
@@ -6266,7 +6266,7 @@
         <v>45322</v>
       </c>
       <c r="B218" t="n">
-        <v>229.6101226806641</v>
+        <v>229.6101379394531</v>
       </c>
       <c r="C218" t="n">
         <v>243.9299926757812</v>
@@ -6324,7 +6324,7 @@
         <v>45382</v>
       </c>
       <c r="B220" t="n">
-        <v>232.6869659423828</v>
+        <v>232.6869812011719</v>
       </c>
       <c r="C220" t="n">
         <v>245.9299926757812</v>
@@ -6353,7 +6353,7 @@
         <v>45412</v>
       </c>
       <c r="B221" t="n">
-        <v>224.3892364501953</v>
+        <v>224.3892211914062</v>
       </c>
       <c r="C221" t="n">
         <v>237.1600036621094</v>
@@ -6382,7 +6382,7 @@
         <v>45443</v>
       </c>
       <c r="B222" t="n">
-        <v>221.5392608642578</v>
+        <v>221.539306640625</v>
       </c>
       <c r="C222" t="n">
         <v>232.8200073242188</v>
@@ -6498,7 +6498,7 @@
         <v>45565</v>
       </c>
       <c r="B226" t="n">
-        <v>235.7852325439453</v>
+        <v>235.7852172851562</v>
       </c>
       <c r="C226" t="n">
         <v>246.4799957275391</v>
@@ -6527,7 +6527,7 @@
         <v>45596</v>
       </c>
       <c r="B227" t="n">
-        <v>222.0005035400391</v>
+        <v>222.0005187988281</v>
       </c>
       <c r="C227" t="n">
         <v>232.0700073242188</v>
@@ -6556,7 +6556,7 @@
         <v>45626</v>
       </c>
       <c r="B228" t="n">
-        <v>234.0442047119141</v>
+        <v>234.044189453125</v>
       </c>
       <c r="C228" t="n">
         <v>244.6600036621094</v>
@@ -6614,7 +6614,7 @@
         <v>45688</v>
       </c>
       <c r="B230" t="n">
-        <v>238.4061279296875</v>
+        <v>238.4061126708984</v>
       </c>
       <c r="C230" t="n">
         <v>247.7899932861328</v>
@@ -6643,7 +6643,7 @@
         <v>45716</v>
       </c>
       <c r="B231" t="n">
-        <v>238.6527252197266</v>
+        <v>238.6527099609375</v>
       </c>
       <c r="C231" t="n">
         <v>246.6900024414062</v>
@@ -6701,7 +6701,7 @@
         <v>45777</v>
       </c>
       <c r="B233" t="n">
-        <v>208.6336975097656</v>
+        <v>208.6336822509766</v>
       </c>
       <c r="C233" t="n">
         <v>215.6600036621094</v>
@@ -6730,7 +6730,7 @@
         <v>45808</v>
       </c>
       <c r="B234" t="n">
-        <v>215.7374420166016</v>
+        <v>215.7374267578125</v>
       </c>
       <c r="C234" t="n">
         <v>221.6600036621094</v>
@@ -6817,7 +6817,7 @@
         <v>45900</v>
       </c>
       <c r="B237" t="n">
-        <v>218.9553375244141</v>
+        <v>218.955322265625</v>
       </c>
       <c r="C237" t="n">
         <v>223.5700073242188</v>
@@ -6875,7 +6875,7 @@
         <v>45961</v>
       </c>
       <c r="B239" t="n">
-        <v>215.8213653564453</v>
+        <v>215.8213806152344</v>
       </c>
       <c r="C239" t="n">
         <v>220.3699951171875</v>
@@ -7049,7 +7049,7 @@
         <v>46142</v>
       </c>
       <c r="B245" t="n">
-        <v>266.8488464355469</v>
+        <v>266.8488159179688</v>
       </c>
       <c r="C245" t="n">
         <v>269.4800109863281</v>
